--- a/data/checks-planejamento.xlsx
+++ b/data/checks-planejamento.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B667"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -370,60 +370,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_composite_primary_key_indicadores</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A ação 2108, uo 1251, consta como deletada na base ações-planejamento (desc.: FORTALECIMENTO DO ...) em inconsistência com a base localizadores (NA).</t>
+          <t>Linha contém valores ausentes ou duplicados na chave programa_cod = 101, programa_cod = 101, 
+is_deleted_programa = FALSE, indicador = PROJETOS MULTISSETORIAIS DE RESILIÊNCIA HÍDRICA, is_deleted_indicador = FALSE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_composite_primary_key_indicadores</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A ação 2500, uo 1261, consta como deletada na base ações-planejamento (desc.: ASSESSORAMENTO E ...) em inconsistência com a base localizadores (NA).</t>
+          <t>Linha contém valores ausentes ou duplicados na chave programa_cod = 101, programa_cod = 101, 
+is_deleted_programa = FALSE, indicador = PROJETOS MULTISSETORIAIS DE RESILIÊNCIA HÍDRICA, is_deleted_indicador = FALSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_composite_primary_key_indicadores</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A ação 4161, uo 1321, consta como deletada na base ações-planejamento (desc.: VIGILÂNCIA DA ...) em inconsistência com a base localizadores (NA).</t>
+          <t>Linha contém valores ausentes ou duplicados na chave programa_cod = 101, programa_cod = 101, 
+is_deleted_programa = FALSE, indicador = PROJETOS MULTISSETORIAIS DE RESILIÊNCIA HÍDRICA, is_deleted_indicador = FALSE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_count_programas_is_deleted</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A ação 4177, uo 1321, consta como deletada na base ações-planejamento (desc.: VIGILÂNCIA DA ...) em inconsistência com a base localizadores (NA).</t>
+          <t>O programa 140 consta como deletado na base programas, porém não nas bases ações-planejamento e localizadores.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_count_programas_is_deleted</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A ação 1026, uo 2421, consta como deletada na base ações-planejamento (desc.: PROMOÇÃO DE ...) em inconsistência com a base localizadores (NA).</t>
+          <t>O programa 144 consta como deletado na base programas, porém não nas bases ações-planejamento e localizadores.</t>
         </is>
       </c>
     </row>
@@ -435,7 +438,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A ação 1027, uo 2421, consta como deletada na base ações-planejamento (desc.: PROMOÇÃO DE ...) em inconsistência com a base localizadores (NA).</t>
+          <t>A ação 1085, uo 1501, consta como deletada na base ações-planejamento (desc.: ABRIGOS E ...) em inconsistência com a base localizadores (NA).</t>
         </is>
       </c>
     </row>
@@ -447,7 +450,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A ação 1029, uo 2421, consta como deletada na base ações-planejamento (desc.: PROMOÇÃO DE ...) em inconsistência com a base localizadores (NA).</t>
+          <t>A ação 4306, uo 1521, consta como deletada na base ações-planejamento (desc.: FOMENTO AO ...) em inconsistência com a base localizadores (NA).</t>
         </is>
       </c>
     </row>
@@ -459,7 +462,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A ação 1031, uo 2421, consta como deletada na base ações-planejamento (desc.: PROMOÇÃO DE ...) em inconsistência com a base localizadores (NA).</t>
+          <t>A ação 4313, uo 1521, consta como deletada na base ações-planejamento (desc.: COORDENAÇÃO DAS ...) em inconsistência com a base localizadores (NA).</t>
         </is>
       </c>
     </row>
@@ -471,2155 +474,7936 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A ação 2417, uo 2421, consta como deletada na base ações-planejamento (desc.: REMUNERAÇÃO DE ...) em inconsistência com a base localizadores (NA).</t>
+          <t>A ação 3012, uo 5081, consta como deletada na base ações-planejamento (desc.: DOAÇÃO DE ...) em inconsistência com a base localizadores (NA).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A ação 2417, uo 2471, consta como deletada na base ações-planejamento (desc.: REMUNERAÇÃO DE ...) em inconsistência com a base localizadores (NA).</t>
+          <t>A ação 2060, na uo 1251, funcional-programática 10.302.135, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 4.257.085,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A ação 2500, uo 2471, consta como deletada na base ações-planejamento (desc.: ASSESSORAMENTO E ...) em inconsistência com a base localizadores (NA).</t>
+          <t>A ação 1037, na uo 1301, funcional-programática 15.451.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 27.633.026,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A ação 1034, uo 3041, consta como deletada na base ações-planejamento (desc.: MELHORAMENTO GENÉTICO ...) em inconsistência com a base localizadores (NA).</t>
+          <t>A ação 1038, na uo 1301, funcional-programática 15.451.099, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 2.062.697,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 10 está com os valores totais de receita e despesa diferentes nas bases. R$ 84.363.501.073,00 na base orçamento fiscal da receita, e 90.656.750.925,00 na qdd fiscal. A diferença é de R$ -6293249852.</t>
+          <t>A ação 1039, na uo 1301, funcional-programática 15.451.139, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 4.865.499,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 12 está com os valores totais de receita e despesa diferentes nas bases. R$ 444,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 444.</t>
+          <t>A ação 1041, na uo 1301, funcional-programática 15.451.139, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 6.479.795,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 20 está com os valores totais de receita e despesa diferentes nas bases. R$ 0,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ NA.</t>
+          <t>A ação 4441, na uo 1451, funcional-programática 06.243.146, iag 1, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 29.000.001,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 31 está com os valores totais de receita e despesa diferentes nas bases. R$ 77.971.087,00 na base orçamento fiscal da receita, e 57.420.824,00 na qdd fiscal. A diferença é de R$ 20550263.</t>
+          <t>A ação 1048, na uo 1451, funcional-programática 06.421.130, iag 1, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 904.245,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 40 está com os valores totais de receita e despesa diferentes nas bases. R$ 392.059,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 392059.</t>
+          <t>A ação 4063, na uo 1511, funcional-programática 06.181.032, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 150.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 46 está com os valores totais de receita e despesa diferentes nas bases. R$ 2.072,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 2072.</t>
+          <t>A ação 4058, na uo 2101, funcional-programática 18.541.031, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 350.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 47 está com os valores totais de receita e despesa diferentes nas bases. R$ 28.687.328,00 na base orçamento fiscal da receita, e 14.640.082,00 na qdd fiscal. A diferença é de R$ 14047246.</t>
+          <t>A ação 4059, na uo 2101, funcional-programática 18.541.031, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 1.000.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 52 está com os valores totais de receita e despesa diferentes nas bases. R$ 52.340.332,00 na base orçamento fiscal da receita, e 24.743.178,00 na qdd fiscal. A diferença é de R$ 27597154.</t>
+          <t>A ação 4268, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 10.000.000,00 na qdd-fiscal e R$ 251.721.140,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 53 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.600,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 1600.</t>
+          <t>A ação 4272, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 49.194.754,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 54 está com os valores totais de receita e despesa diferentes nas bases. R$ 6.682.512,00 na base orçamento fiscal da receita, e 4.104.010,00 na qdd fiscal. A diferença é de R$ 2578502.</t>
+          <t>A ação 4275, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 56.282.273,00 na qdd-fiscal e R$ 251.008.739,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 59 está com os valores totais de receita e despesa diferentes nas bases. R$ 383.447.752,00 na base orçamento fiscal da receita, e 342.620.315,00 na qdd fiscal. A diferença é de R$ 40827437.</t>
+          <t>A ação 4287, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 1.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 60 está com os valores totais de receita e despesa diferentes nas bases. R$ 4.528.328.118,00 na base orçamento fiscal da receita, e 3.795.212.434,00 na qdd fiscal. A diferença é de R$ 733115684.</t>
+          <t>A ação 4289, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 1.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 61 está com os valores totais de receita e despesa diferentes nas bases. R$ 433.782.405,00 na base orçamento fiscal da receita, e 406.710.026,00 na qdd fiscal. A diferença é de R$ 27072379.</t>
+          <t>A ação 4293, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 690.658.203,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 72 está com os valores totais de receita e despesa diferentes nas bases. R$ 456.921.538,00 na base orçamento fiscal da receita, e 350.859.025,00 na qdd fiscal. A diferença é de R$ 106062513.</t>
+          <t>A ação 4385, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 32.000.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 79 está com os valores totais de receita e despesa diferentes nas bases. R$ 7.765.658,00 na base orçamento fiscal da receita, e 4.000.000,00 na qdd fiscal. A diferença é de R$ 3765658.</t>
+          <t>A ação 4280, na uo 2301, funcional-programática 26.782.139, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 9.000.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 83 está com os valores totais de receita e despesa diferentes nas bases. R$ 205.514.880,00 na base orçamento fiscal da receita, e 175.581.839,00 na qdd fiscal. A diferença é de R$ 29933041.</t>
+          <t>A ação 4238, na uo 2371, funcional-programática 20.609.078, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 8.311.374,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 91 está com os valores totais de receita e despesa diferentes nas bases. R$ 133.921.299,00 na base orçamento fiscal da receita, e 69.063.939,00 na qdd fiscal. A diferença é de R$ 64857360.</t>
+          <t>A ação 1016, na uo 2421, funcional-programática 08.544.101, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 477.508,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 94 está com os valores totais de receita e despesa diferentes nas bases. R$ 10.715.576,00 na base orçamento fiscal da receita, e 6.760.698,00 na qdd fiscal. A diferença é de R$ 3954878.</t>
+          <t>A ação 2060, na UO 1251, funcional-programática 10.302.135 iag 0, está com valores diferentes entre as bases, R$ 4.257.085,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>O programa 2 contém indicador (PERCENTUAL DE INSTITUCIONALIZAÇÃO...) que, apesar de ter índice de referência de 100, está sem meta para o ano 0.</t>
+          <t>A ação 1037, na UO 1301, funcional-programática 15.451.081 iag 0, está com valores diferentes entre as bases, R$ 158.935.952,00 na qdd-fiscal e R$ 131.302.926,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>O programa 3 contém indicador (ÍNDICE DE EFETIVIDADE...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 1038, na UO 1301, funcional-programática 15.451.099 iag 0, está com valores diferentes entre as bases, R$ 5.332.352,00 na qdd-fiscal e R$ 3.269.655,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>O programa 11 contém indicador (TAXA DE MATERIAIS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 1039, na UO 1301, funcional-programática 15.451.139 iag 0, está com valores diferentes entre as bases, R$ 4.865.499,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>O programa 18 contém indicador (NUMERO DE MATÉRIAS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 1041, na UO 1301, funcional-programática 15.451.139 iag 0, está com valores diferentes entre as bases, R$ 9.208.378,00 na qdd-fiscal e R$ 2.728.583,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>O programa 27 contém indicador (INCREMENTO DE ABRANGÊNCIA...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4441, na UO 1451, funcional-programática 06.243.146 iag 1, está com valores diferentes entre as bases, R$ 29.000.001,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>O programa 27 contém indicador (ABRANGÊNCIA DOS PROGRAMAS,...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 1048, na UO 1451, funcional-programática 06.421.130 iag 1, está com valores diferentes entre as bases, R$ 45.212.295,00 na qdd-fiscal e R$ 44.308.050,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>O programa 27 contém indicador (EXECUÇÃO DAS METAS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4063, na UO 1511, funcional-programática 06.181.032 iag 0, está com valores diferentes entre as bases, R$ 20.000.000,00 na qdd-fiscal e R$ 19.850.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>O programa 81 contém indicador (EVOLUÇÃO DA QUALIDADE...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4058, na UO 2101, funcional-programática 18.541.031 iag 0, está com valores diferentes entre as bases, R$ 350.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>O programa 91 contém indicador (DISCENTES FORMADOS E...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4059, na UO 2101, funcional-programática 18.541.031 iag 0, está com valores diferentes entre as bases, R$ 1.000.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>O programa 91 contém indicador (GRAU DE SATISFAÇÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4268, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 261.721.140,00 na qdd-fiscal e R$ 20.000.000,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>O programa 91 contém indicador (ARTIGOS ACADÊMICOS ACEITOS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4272, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 49.194.754,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>O programa 99 contém indicador (ÍNDICE ACUMULADO DE...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4275, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 361.913.350,00 na qdd-fiscal e R$ 167.186.884,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>O programa 172 contém indicador (PERCENTUAL DE EXECUÇÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4287, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 1.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>O programa 172 contém indicador (PERCENTUAL DE OBRAS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4289, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 1.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>O programa 746 contém indicador (QUANTIDADE DE INDÍCIOS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4293, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 777.948.268,00 na qdd-fiscal e R$ 87.290.065,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>O programa 746 contém indicador (ÍNDICE DE IRREGULARIDADES...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A ação 4385, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 32.000.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>check_indicadores_indice_referencia_data_futura</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>O programa 64 contém indicador (NÚMERO DE MUNICÍPIOS...) cujo índice de referência, apesar de não estar em apuração, apresenta data de apuração futura: 2025-12-31.</t>
+          <t>A ação 4280, na UO 2301, funcional-programática 26.782.139 iag 0, está com valores diferentes entre as bases, R$ 9.000.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>O programa 92 contém indicador (TAXA DE EXPANSÃO...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A ação 4238, na UO 2371, funcional-programática 20.609.078 iag 0, está com valores diferentes entre as bases, R$ 8.311.374,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>O programa 94 contém indicador (TAXA DE CRESCIMENTO...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A ação 1016, na UO 2421, funcional-programática 08.544.101 iag 0, está com valores diferentes entre as bases, R$ 477.508,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>O programa 165 contém indicador (IDEB ANOS INICIAIS...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A Fonte de Recurso 10 está com os valores totais de receita e despesa diferentes nas bases. R$ 86.813.437.501,00 na base orçamento fiscal da receita, e 91.514.592.757,00 na qdd fiscal. A diferença é de R$ -4701155256.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>O programa 165 contém indicador (IDEB ENSINO MÉDIO...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A Fonte de Recurso 12 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.000,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 1000.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>O programa 165 contém indicador (IDEB ANOS FINAIS...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A Fonte de Recurso 20 está com os valores totais de receita e despesa diferentes nas bases. R$ 0,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>O programa 167 contém indicador (IDEB ANOS INICIAIS...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A Fonte de Recurso 31 está com os valores totais de receita e despesa diferentes nas bases. R$ 87.761.794,00 na base orçamento fiscal da receita, e 65.836.031,00 na qdd fiscal. A diferença é de R$ 21925763.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>O programa 167 contém indicador (IDEB ENSINO MÉDIO...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A Fonte de Recurso 40 está com os valores totais de receita e despesa diferentes nas bases. R$ 203.859,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 203859.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>O programa 167 contém indicador (IDEB ANOS FINAIS...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A Fonte de Recurso 46 está com os valores totais de receita e despesa diferentes nas bases. R$ 2.901,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 2901.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A uo 1401 está com valor recebido de recursos intraorçamentários (R$ 960.756,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 47 está com os valores totais de receita e despesa diferentes nas bases. R$ 35.242.116,00 na base orçamento fiscal da receita, e 31.436.436,00 na qdd fiscal. A diferença é de R$ 3805680.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A uo 1451 está com valor recebido de recursos intraorçamentários (R$ 224.346.201,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 48 está com os valores totais de receita e despesa diferentes nas bases. R$ 327.327.763,00 na base orçamento fiscal da receita, e 7.207.328.033,00 na qdd fiscal. A diferença é de R$ -6880000270.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A uo 1541 está com valor recebido de recursos intraorçamentários (R$ 31.538.282,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 52 está com os valores totais de receita e despesa diferentes nas bases. R$ 55.754.000,00 na base orçamento fiscal da receita, e 23.650.000,00 na qdd fiscal. A diferença é de R$ 32104000.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A uo 2011 está com valor recebido de recursos intraorçamentários (R$ 647.702.182,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 53 está com os valores totais de receita e despesa diferentes nas bases. R$ 2.000,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 2000.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A uo 2121 está com valor recebido de recursos intraorçamentários (R$ 2.260.804.301,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 59 está com os valores totais de receita e despesa diferentes nas bases. R$ 455.621.137,00 na base orçamento fiscal da receita, e 388.170.423,00 na qdd fiscal. A diferença é de R$ 67450714.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A uo 2251 está com valor recebido de recursos intraorçamentários (R$ 18.000,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 60 está com os valores totais de receita e despesa diferentes nas bases. R$ 4.506.993.690,00 na base orçamento fiscal da receita, e 5.326.603.517,00 na qdd fiscal. A diferença é de R$ -819609827.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A uo 2261 está com valor recebido de recursos intraorçamentários (R$ 652.857.538,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 61 está com os valores totais de receita e despesa diferentes nas bases. R$ 510.759.469,00 na base orçamento fiscal da receita, e 454.124.918,00 na qdd fiscal. A diferença é de R$ 56634551.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A uo 2271 está com valor recebido de recursos intraorçamentários (R$ 2.397.229.409,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 72 está com os valores totais de receita e despesa diferentes nas bases. R$ 470.959.523,00 na base orçamento fiscal da receita, e 378.466.043,00 na qdd fiscal. A diferença é de R$ 92493480.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A uo 2321 está com valor recebido de recursos intraorçamentários (R$ 487.249.378,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 79 está com os valores totais de receita e despesa diferentes nas bases. R$ 16.160.491,00 na base orçamento fiscal da receita, e 3.369.600,00 na qdd fiscal. A diferença é de R$ 12790891.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A uo 2361 está com valor recebido de recursos intraorçamentários (R$ 15.037.000,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 80 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.019.599.103,00 na base orçamento fiscal da receita, e 778.721.696,00 na qdd fiscal. A diferença é de R$ 240877407.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A uo 3051 está com valor recebido de recursos intraorçamentários (R$ 660.084,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 91 está com os valores totais de receita e despesa diferentes nas bases. R$ 149.914.755,00 na base orçamento fiscal da receita, e 95.820.233,00 na qdd fiscal. A diferença é de R$ 54094522.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A uo 4031 está com valor recebido de recursos intraorçamentários (R$ 87.655.976,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 94 está com os valores totais de receita e despesa diferentes nas bases. R$ 10.873.232,00 na base orçamento fiscal da receita, e 7.321.724,00 na qdd fiscal. A diferença é de R$ 3551508.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A uo 4631 está com valor recebido de recursos intraorçamentários (R$ 1.000,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 95 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.312.851.799,00 na base orçamento fiscal da receita, e 750.000,00 na qdd fiscal. A diferença é de R$ 1312101799.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A uo 4661 está com valor recebido de recursos intraorçamentários (R$ 470.000,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso NA está com os valores totais de receita e despesa diferentes nas bases. R$ 9.290.788.295,00 na base receita de investimento, e R$  NA na qdd investimento. A diferença é de R$ 9290788295.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A uo 4711 está com valor recebido de recursos intraorçamentários (R$ 7.218.864.598,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 11101 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 4.000,00 na qdd investimento. A diferença é de R$ 4000.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A uo 9901 está com valor recebido de recursos intraorçamentários (R$ 580.295.911,00) diferente do valor detalhado (R$ 0,00) na base intra-detalhamento.</t>
+          <t>A Fonte de Recurso 12400 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 1.123.941.920,00 na qdd investimento. A diferença é de R$ 1123941920.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$ (15.387,00) entre o valor de limite no ano 0 (R$ 12.495.112,00) e a soma do valor utilizado no ano (R$ 12.510.499,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 12.510.499,00.</t>
+          <t>A Fonte de Recurso 51000 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 8.166.842.375,00 na qdd investimento. A diferença é de R$ 8166842375.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$ (1.000,00) entre o valor de limite no ano 0 (R$ 29.425.835,00) e a soma do valor utilizado no ano (R$ 29.426.835,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 29.426.835,00.</t>
+          <t>O programa 6 contém indicador (GASTO PER CAPITA...) que, apesar de ter índice de referência de 384524, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$ (150.714.182,00) entre o valor de limite no ano 0 (R$ 353.708.669,00) e a soma do valor utilizado no ano (R$ 504.422.851,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 504.422.851,00.</t>
+          <t>O programa 165 contém indicador (IDEB ANOS INICIAIS...) que, apesar de ter índice de referência de 63, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$ (1.778.147,00) entre o valor de limite no ano 0 (R$ 41.116.142,00) e a soma do valor utilizado no ano (R$ 42.894.289,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 42.894.289,00.</t>
+          <t>O programa 165 contém indicador (IDEB ANOS FINAIS...) que, apesar de ter índice de referência de 46, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A uo 2171 está com uma diferença de R$ (45.346,00) entre o valor de limite no ano 0 (R$ 1.145.946,00) e a soma do valor utilizado no ano (R$ 1.191.292,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 1.191.292,00.</t>
+          <t>O programa 165 contém indicador (IDEB ENSINO MÉDIO...) que, apesar de ter índice de referência de 4, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A uo 2171 está com uma diferença de R$ (2.000,00) entre o valor de limite no ano 0 (R$ 2.641.831,00) e a soma do valor utilizado no ano (R$ 2.643.831,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 2.643.831,00.</t>
+          <t>O programa 167 contém indicador (IDEB ANOS INICIAIS...) que, apesar de ter índice de referência de 63, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$ (26.250,00) entre o valor de limite no ano 0 (R$ 87.500,00) e a soma do valor utilizado no ano (R$ 113.750,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 113.750,00.</t>
+          <t>O programa 167 contém indicador (IDEB ENSINO MÉDIO...) que, apesar de ter índice de referência de 4, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$ 1.034.956.298,00 entre o valor de limite no ano 0 (R$ 1.389.694.094,00) e a soma do valor utilizado no ano (R$ 354.737.796,00) com o valor transferido no ano (R$ 0,00), que totalizam R$ 354.737.796,00.</t>
+          <t>O programa 167 contém indicador (IDEB ANOS FINAIS...) que, apesar de ter índice de referência de 46, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>O programa 98 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 3 contém indicador (ÍNDICE DE EFETIVIDADE...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>O programa 704 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 36 contém indicador (Unidade de identidade...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>O programa 706 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 91 contém indicador (DISCENTES FORMADOS E...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>O programa 726 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 91 contém indicador (GRAU DE SATISFAÇÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>O programa 729 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 91 contém indicador (ARTIGOS ACADÊMICOS ACEITOS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>O programa 734 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 160 contém indicador (EFICÁCIA DA GESTÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_justificativa_previsao_em_apuracao</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>O programa 738 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 6 contém indicador (GASTO PER CAPITA...) que, apesar de estar sem previsão para o ano 3, apresenta justificativa de previsão inválida, com menos de 50 caracteres (0 caract.).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_previsoes_exists</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>O programa 746 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 6 contém indicador (GASTO PER CAPITA...) cuja previsão, apesar de não estar em apuração, está sem valor para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_previsoes_zeradas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>O programa 760 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>O programa 6 contém indicador (GASTO PER CAPITA...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_intra_despesa</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>O programa 764 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>A uo 1271, na ação 2417, grupo 1, elemento-item 1321, possui inconsistência nos valores da despesa intraorçamentária (modalidade 91) da base despesa-item fiscal (R$ 272.259,00) e da base intra-repasse (R$ 230.431,00).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_intra_despesa</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>O programa 765 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>A uo 1271, na ação 2417, grupo 1, elemento-item 1326, possui inconsistência nos valores da despesa intraorçamentária (modalidade 91) da base despesa-item fiscal (R$ 2.672.505,00) e da base intra-repasse (R$ 2.714.333,00).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>O programa 766 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>A uo 2011 está com valor recebido de recursos intraorçamentários (R$ 617.928.493,00) diferente do valor detalhado (R$ 1.258.967.529,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>O programa 767 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+          <t>A uo 2121 está com valor recebido de recursos intraorçamentários (R$ 2.440.013.976,00) diferente do valor detalhado (R$ 2.651.552.847,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>check_ods_exists</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>O programa 8 está sem objetivo de desenvolvimento estratégico definido.</t>
+          <t>A uo 2261 está com valor recebido de recursos intraorçamentários (R$ 662.950.136,00) diferente do valor detalhado (R$ 668.915.291,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>check_ods_exists</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>O programa 126 está sem objetivo de desenvolvimento estratégico definido.</t>
+          <t>A uo 2321 está com valor recebido de recursos intraorçamentários (R$ 494.081.184,00) diferente do valor detalhado (R$ 496.238.756,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>check_ods_exists</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>O programa 138 está sem objetivo de desenvolvimento estratégico definido.</t>
+          <t>A uo 2361 está com valor recebido de recursos intraorçamentários (R$ 15.037.000,00) diferente do valor detalhado (R$ 135.037.000,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>check_ods_exists</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>O programa 142 está sem objetivo de desenvolvimento estratégico definido.</t>
+          <t>A uo 4711 está com valor recebido de recursos intraorçamentários (R$ 7.976.441.576,00) diferente do valor detalhado (R$ 6.558.973.245,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>check_setor_governo</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>A uo 1321 está com setor divergente na base ações-planejamento (SAÚDE) em relação à tabela auxiliar setor-governo da loa (NA).</t>
+          <t>A uo 9901 está com valor recebido de recursos intraorçamentários (R$ 648.487.316,00) diferente do valor detalhado (R$ 941.204.042,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>check_setor_governo</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>A uo 1917 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (FAZENDA).</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.287.437.285,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>check_setor_governo</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A uo 4171 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (AGRICULTURA, PECUÁRIA E ABASTECIMENTO).</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 354.200.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>check_setor_governo</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A uo 4531 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (DESENVOLVIMENTO ECONÔMICO).</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A uo 1021, programa 746, ação 2009, função 1, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 199.226.735,00) diferente da base ações-planejamento (R$ 202.637.401,00). Diferença de R$ -3410666.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 344.471.800,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A uo 1021, programa 760, ação 2145, função 1, subfunção 128 está com valor do ano 0, base qdd-plurianual (R$ 8.462.193,00) diferente da base ações-planejamento (R$ 12.662.193,00). Diferença de R$ -4200000.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 135.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A uo 1071, programa 48, ação 4155, função 6, subfunção 182 está com valor do ano 0, base qdd-plurianual (R$ 131.000,00) diferente da base ações-planejamento (R$ 1.731.000,00). Diferença de R$ -1600000.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 30.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A uo 1071, programa 101, ação 1008, função 6, subfunção 182 está com valor do ano 0, base qdd-plurianual (R$ 14.800.970,00) diferente da base ações-planejamento (R$ 17.060.970,00). Diferença de R$ -2260000.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A uo 1221, programa 125, ação 1082, função 4, subfunção 127 está com valor do ano 0, base qdd-plurianual (R$ 47.501.208,00) diferente da base ações-planejamento (R$ 48.281.208,00). Diferença de R$ -780000.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.953.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A uo 1221, programa 132, ação 4474, função 23, subfunção 691 está com valor do ano 0, base qdd-plurianual (R$ 617.333,00) diferente da base ações-planejamento (R$ 1.117.333,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 714.778.494,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 108, ação 4358, função 20, subfunção 608 está com valor do ano 0, base qdd-plurianual (R$ 9.441.948,00) diferente da base ações-planejamento (R$ 11.326.448,00). Diferença de R$ -1884500.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 319.899.495,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 110, ação 4363, função 21, subfunção 605 está com valor do ano 0, base qdd-plurianual (R$ 8.311.853,00) diferente da base ações-planejamento (R$ 9.061.853,00). Diferença de R$ -750000.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 161.811.560,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 111, ação 4383, função 20, subfunção 608 está com valor do ano 0, base qdd-plurianual (R$ 13.387.942,00) diferente da base ações-planejamento (R$ 13.537.942,00). Diferença de R$ -150000.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 95.102.996,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 111, ação 4420, função 20, subfunção 608 está com valor do ano 0, base qdd-plurianual (R$ 30.000.000,00) diferente da base ações-planejamento (R$ 53.592.878,00). Diferença de R$ -23592878.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 112, ação 4403, função 20, subfunção 608 está com valor do ano 0, base qdd-plurianual (R$ 5.720.025,00) diferente da base ações-planejamento (R$ 5.810.235,00). Diferença de R$ -90210.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.752.235,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 114, ação 4398, função 20, subfunção 607 está com valor do ano 0, base qdd-plurianual (R$ 11.866.753,00) diferente da base ações-planejamento (R$ 13.841.359,00). Diferença de R$ -1974606.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.846.022.621,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 114, ação 4419, função 20, subfunção 127 está com valor do ano 0, base qdd-plurianual (R$ 1.377.192,00) diferente da base ações-planejamento (R$ 2.377.192,00). Diferença de R$ -1e+06.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.073.299.042,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>A uo 1231, programa 705, ação 2500, função 20, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 12.430.883,00) diferente da base ações-planejamento (R$ 13.930.883,00). Diferença de R$ -1500000.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>A uo 1251, programa 137, ação 4365, função 6, subfunção 181 está com valor do ano 0, base qdd-plurianual (R$ 6.334.166.724,00) diferente da base ações-planejamento (R$ 6.334.866.724,00). Diferença de R$ -7e+05.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 908.022.281,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>A uo 1251, programa 137, ação 4366, função 6, subfunção 181 está com valor do ano 0, base qdd-plurianual (R$ 1.050,00) diferente da base ações-planejamento (R$ 40.343.178,00). Diferença de R$ -40342128.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 399.038.512,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>A uo 1251, programa 137, ação 4373, função 6, subfunção 181 está com valor do ano 0, base qdd-plurianual (R$ 3.600,00) diferente da base ações-planejamento (R$ 103.600,00). Diferença de R$ -1e+05.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 115.458.254,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>A uo 1251, programa 705, ação 2500, função 6, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 376.861.077,00) diferente da base ações-planejamento (R$ 378.361.077,00). Diferença de R$ -1500000.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.303.609,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>A uo 1261, programa 167, ação 2122, função 12, subfunção 361 está com valor do ano 0, base qdd-plurianual (R$ 117.100.000,00) diferente da base ações-planejamento (R$ 118.550.000,00). Diferença de R$ -1450000.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>A uo 1261, programa 167, ação 4511, função 12, subfunção 362 está com valor do ano 0, base qdd-plurianual (R$ 62.600.000,00) diferente da base ações-planejamento (R$ 66.600.000,00). Diferença de R$ -4e+06.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.324.521,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>A uo 1261, programa 168, ação 2126, função 12, subfunção 368 está com valor do ano 0, base qdd-plurianual (R$ 456.147.344,00) diferente da base ações-planejamento (R$ 553.858.039,00). Diferença de R$ -97710695.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.064.254,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>A uo 1261, programa 168, ação 4519, função 12, subfunção 368 está com valor do ano 0, base qdd-plurianual (R$ 524.704.215,00) diferente da base ações-planejamento (R$ 534.715.902,00). Diferença de R$ -10011687.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.097.663,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>A uo 1261, programa 168, ação 4527, função 12, subfunção 368 está com valor do ano 0, base qdd-plurianual (R$ 644.976.000,00) diferente da base ações-planejamento (R$ 650.592.317,00). Diferença de R$ -5616317.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>A uo 1261, programa 172, ação 4545, função 12, subfunção 361 está com valor do ano 0, base qdd-plurianual (R$ 45.000.000,00) diferente da base ações-planejamento (R$ 45.324.049,00). Diferença de R$ -324049.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.628.259,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>A uo 1271, programa 102, ação 4332, função 13, subfunção 392 está com valor do ano 0, base qdd-plurianual (R$ 33.144.232,00) diferente da base ações-planejamento (R$ 49.994.232,00). Diferença de R$ -16850000.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.609.120,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>A uo 1271, programa 102, ação 4343, função 13, subfunção 392 está com valor do ano 0, base qdd-plurianual (R$ 170.568.000,00) diferente da base ações-planejamento (R$ 170.569.000,00). Diferença de R$ -1000.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>A uo 1271, programa 103, ação 4322, função 13, subfunção 392 está com valor do ano 0, base qdd-plurianual (R$ 10.500.000,00) diferente da base ações-planejamento (R$ 10.800.000,00). Diferença de R$ -3e+05.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.580.735,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>A uo 1271, programa 705, ação 2500, função 13, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 2.820.327,00) diferente da base ações-planejamento (R$ 3.320.327,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 87.750,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>A uo 1301, programa 99, ação 4261, função 15, subfunção 451 está com valor do ano 0, base qdd-plurianual (R$ 7.140.411,00) diferente da base ações-planejamento (R$ 10.140.411,00). Diferença de R$ -3e+06.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 395.202.978,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>A uo 1301, programa 99, ação 4262, função 15, subfunção 451 está com valor do ano 0, base qdd-plurianual (R$ 16.016.092,00) diferente da base ações-planejamento (R$ 35.016.092,00). Diferença de R$ -1.9e+07.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 658.905.647,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>A uo 1371, programa 21, ação 4028, função 17, subfunção 512 está com valor do ano 0, base qdd-plurianual (R$ 50.231.475,00) diferente da base ações-planejamento (R$ 51.439.475,00). Diferença de R$ -1208000.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.516.568,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>A uo 1371, programa 21, ação 4044, função 17, subfunção 512 está com valor do ano 0, base qdd-plurianual (R$ 3.819.644,00) diferente da base ações-planejamento (R$ 4.219.644,00). Diferença de R$ -4e+05.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.676.685,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>A uo 1371, programa 27, ação 4045, função 18, subfunção 541 está com valor do ano 0, base qdd-plurianual (R$ 807.634,00) diferente da base ações-planejamento (R$ 2.807.634,00). Diferença de R$ -2e+06.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 224.961.893,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>A uo 1371, programa 27, ação 4046, função 18, subfunção 541 está com valor do ano 0, base qdd-plurianual (R$ 557.957,00) diferente da base ações-planejamento (R$ 558.957,00). Diferença de R$ -1000.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.697.432,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>A uo 1371, programa 27, ação 4047, função 18, subfunção 541 está com valor do ano 0, base qdd-plurianual (R$ 685.640,00) diferente da base ações-planejamento (R$ 34.385.640,00). Diferença de R$ -33700000.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.042.666.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>A uo 1371, programa 27, ação 4124, função 18, subfunção 541 está com valor do ano 0, base qdd-plurianual (R$ 3.200.000,00) diferente da base ações-planejamento (R$ 4.000.000,00). Diferença de R$ -8e+05.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 111.710.700,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>A uo 1401, programa 52, ação 4114, função 6, subfunção 182 está com valor do ano 0, base qdd-plurianual (R$ 486.636.314,00) diferente da base ações-planejamento (R$ 494.723.314,00). Diferença de R$ -8087000.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>A uo 1401, programa 52, ação 4115, função 6, subfunção 182 está com valor do ano 0, base qdd-plurianual (R$ 687.674.923,00) diferente da base ações-planejamento (R$ 688.174.923,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 459.800.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>A uo 1401, programa 52, ação 4120, função 6, subfunção 182 está com valor do ano 0, base qdd-plurianual (R$ 11.030.599,00) diferente da base ações-planejamento (R$ 14.160.599,00). Diferença de R$ -3130000.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 338.713.676,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>A uo 1401, programa 52, ação 4138, função 18, subfunção 182 está com valor do ano 0, base qdd-plurianual (R$ 11.690.903,00) diferente da base ações-planejamento (R$ 12.690.903,00). Diferença de R$ -1e+06.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.336.775,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>A uo 1401, programa 53, ação 4094, função 10, subfunção 302 está com valor do ano 0, base qdd-plurianual (R$ 960.756,00) diferente da base ações-planejamento (R$ 8.281.747,00). Diferença de R$ -7320991.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.663.225,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>A uo 1451, programa 129, ação 4344, função 6, subfunção 421 está com valor do ano 0, base qdd-plurianual (R$ 51.978.801,00) diferente da base ações-planejamento (R$ 52.679.791,00). Diferença de R$ -700990.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>A uo 1451, programa 130, ação 1048, função 6, subfunção 421 está com valor do ano 0, base qdd-plurianual (R$ 58.811.637,00) diferente da base ações-planejamento (R$ 63.784.579,00). Diferença de R$ -4972942.</t>
+          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.016.356,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>A uo 1451, programa 130, ação 4348, função 6, subfunção 421 está com valor do ano 0, base qdd-plurianual (R$ 735.242.265,00) diferente da base ações-planejamento (R$ 736.174.265,00). Diferença de R$ -932000.</t>
+          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.236.596,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>A uo 1451, programa 130, ação 4351, função 6, subfunção 421 está com valor do ano 0, base qdd-plurianual (R$ 124.967.835,00) diferente da base ações-planejamento (R$ 125.067.835,00). Diferença de R$ -1e+05.</t>
+          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.801.362,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>A uo 1451, programa 141, ação 4438, função 6, subfunção 422 está com valor do ano 0, base qdd-plurianual (R$ 6.775.354,00) diferente da base ações-planejamento (R$ 7.275.354,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.629.148.025,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 66, ação 4153, função 11, subfunção 334 está com valor do ano 0, base qdd-plurianual (R$ 6.876.017,00) diferente da base ações-planejamento (R$ 7.126.017,00). Diferença de R$ -250000.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 314.144.747,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 69, ação 4167, função 27, subfunção 812 está com valor do ano 0, base qdd-plurianual (R$ 1.187.363,00) diferente da base ações-planejamento (R$ 1.687.363,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 82.434.724,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 69, ação 4170, função 27, subfunção 812 está com valor do ano 0, base qdd-plurianual (R$ 1.374.510,00) diferente da base ações-planejamento (R$ 11.159.340,00). Diferença de R$ -9784830.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.800.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 69, ação 4514, função 27, subfunção 812 está com valor do ano 0, base qdd-plurianual (R$ 3.378.169,00) diferente da base ações-planejamento (R$ 3.628.169,00). Diferença de R$ -250000.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.874.808,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 70, ação 4174, função 14, subfunção 422 está com valor do ano 0, base qdd-plurianual (R$ 1.000,00) diferente da base ações-planejamento (R$ 2.001.990,00). Diferença de R$ -2000990.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.173.695,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 74, ação 4196, função 14, subfunção 306 está com valor do ano 0, base qdd-plurianual (R$ 1.242.678,00) diferente da base ações-planejamento (R$ 1.642.678,00). Diferença de R$ -4e+05.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.408.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 86, ação 4415, função 14, subfunção 422 está com valor do ano 0, base qdd-plurianual (R$ 2.622.178,00) diferente da base ações-planejamento (R$ 2.722.178,00). Diferença de R$ -1e+05.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 24.696.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>A uo 1481, programa 148, ação 2079, função 4, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 5.634.602,00) diferente da base ações-planejamento (R$ 16.425.592,00). Diferença de R$ -10790990.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.447.984,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>A uo 1491, programa 119, ação 2045, função 4, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 3.189.678,00) diferente da base ações-planejamento (R$ 98.946.739,00). Diferença de R$ -95757061.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 884.409,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>A uo 1491, programa 119, ação 2048, função 4, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 1.000,00) diferente da base ações-planejamento (R$ 861.067.452,00). Diferença de R$ -861066452.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.962.078,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>A uo 1501, programa 156, ação 4465, função 4, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 95.680.170,00) diferente da base ações-planejamento (R$ 96.243.170,00). Diferença de R$ -563000.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.195.653,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>A uo 1511, programa 32, ação 1006, função 6, subfunção 181 está com valor do ano 0, base qdd-plurianual (R$ 316,00) diferente da base ações-planejamento (R$ 500.316,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 566.797,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>A uo 1511, programa 32, ação 1007, função 6, subfunção 181 está com valor do ano 0, base qdd-plurianual (R$ 1.000,00) diferente da base ações-planejamento (R$ 21.138.490,00). Diferença de R$ -21137490.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.006.091,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>A uo 1511, programa 32, ação 4060, função 6, subfunção 181 está com valor do ano 0, base qdd-plurianual (R$ 158.599.650,00) diferente da base ações-planejamento (R$ 161.249.650,00). Diferença de R$ -2650000.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.604.258,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>A uo 1511, programa 32, ação 4061, função 6, subfunção 181 está com valor do ano 0, base qdd-plurianual (R$ 14.695.363,00) diferente da base ações-planejamento (R$ 14.845.363,00). Diferença de R$ -150000.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 320.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>A uo 2071, programa 22, ação 4513, função 19, subfunção 571 está com valor do ano 0, base qdd-plurianual (R$ 182.314.608,00) diferente da base ações-planejamento (R$ 182.514.607,00). Diferença de R$ -199999.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.666.912,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>A uo 2101, programa 31, ação 4056, função 18, subfunção 543 está com valor do ano 0, base qdd-plurianual (R$ 26.736.707,00) diferente da base ações-planejamento (R$ 27.136.707,00). Diferença de R$ -4e+05.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>A uo 2101, programa 31, ação 4059, função 18, subfunção 541 está com valor do ano 0, base qdd-plurianual (R$ 55.956.871,00) diferente da base ações-planejamento (R$ 57.356.871,00). Diferença de R$ -1400000.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 78.921.382,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>A uo 2201, programa 106, ação 4276, função 13, subfunção 391 está com valor do ano 0, base qdd-plurianual (R$ 63.050,00) diferente da base ações-planejamento (R$ 598.050,00). Diferença de R$ -535000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 22.274.854,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>A uo 2201, programa 106, ação 4278, função 13, subfunção 391 está com valor do ano 0, base qdd-plurianual (R$ 848.458,00) diferente da base ações-planejamento (R$ 1.348.458,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.893.562,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>A uo 2271, programa 19, ação 4031, função 10, subfunção 302 está com valor do ano 0, base qdd-plurianual (R$ 403.048.770,00) diferente da base ações-planejamento (R$ 403.408.770,00). Diferença de R$ -360000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.337.677,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>A uo 2271, programa 19, ação 4036, função 10, subfunção 302 está com valor do ano 0, base qdd-plurianual (R$ 203.935.708,00) diferente da base ações-planejamento (R$ 204.475.708,00). Diferença de R$ -540000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>A uo 2301, programa 81, ação 4268, função 26, subfunção 782 está com valor do ano 0, base qdd-plurianual (R$ 88.091.501,00) diferente da base ações-planejamento (R$ 88.092.501,00). Diferença de R$ -1000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.458.016,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>A uo 2301, programa 81, ação 4275, função 26, subfunção 782 está com valor do ano 0, base qdd-plurianual (R$ 363.158.594,00) diferente da base ações-planejamento (R$ 363.159.594,00). Diferença de R$ -1000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.524.705,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>A uo 2301, programa 81, ação 4293, função 26, subfunção 782 está com valor do ano 0, base qdd-plurianual (R$ 651.192.418,00) diferente da base ações-planejamento (R$ 651.193.418,00). Diferença de R$ -1000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.228.611,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>A uo 2311, programa 7, ação 4002, função 12, subfunção 364 está com valor do ano 0, base qdd-plurianual (R$ 3.958.056,00) diferente da base ações-planejamento (R$ 5.458.056,00). Diferença de R$ -1500000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.823.948,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>A uo 2311, programa 7, ação 4005, função 12, subfunção 364 está com valor do ano 0, base qdd-plurianual (R$ 4.525.088,00) diferente da base ações-planejamento (R$ 9.525.088,00). Diferença de R$ -5e+06.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 307.035,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>A uo 2311, programa 705, ação 2500, função 12, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 10.931.901,00) diferente da base ações-planejamento (R$ 11.431.901,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.251.732,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>A uo 2351, programa 26, ação 4086, função 12, subfunção 364 está com valor do ano 0, base qdd-plurianual (R$ 115.679.715,00) diferente da base ações-planejamento (R$ 117.379.715,00). Diferença de R$ -1700000.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.327.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>A uo 2351, programa 26, ação 4087, função 12, subfunção 364 está com valor do ano 0, base qdd-plurianual (R$ 5.959.778,00) diferente da base ações-planejamento (R$ 5.960.778,00). Diferença de R$ -1000.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.426.625.358,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>A uo 2351, programa 26, ação 4089, função 12, subfunção 364 está com valor do ano 0, base qdd-plurianual (R$ 6.377.753,00) diferente da base ações-planejamento (R$ 10.977.753,00). Diferença de R$ -4600000.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 128.236.192,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>A uo 2351, programa 26, ação 4090, função 12, subfunção 364 está com valor do ano 0, base qdd-plurianual (R$ 24.069.722,00) diferente da base ações-planejamento (R$ 24.909.722,00). Diferença de R$ -840000.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 204.135.476,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>A uo 2421, programa 101, ação 1016, função 8, subfunção 544 está com valor do ano 0, base qdd-plurianual (R$ 4.842.287,00) diferente da base ações-planejamento (R$ 5.957.287,00). Diferença de R$ -1115000.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 648.489.316,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>A uo 2421, programa 101, ação 1032, função 8, subfunção 544 está com valor do ano 0, base qdd-plurianual (R$ 3.206.136,00) diferente da base ações-planejamento (R$ 9.447.126,00). Diferença de R$ -6240990.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.609.779,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>A uo 2421, programa 124, ação 4325, função 20, subfunção 608 está com valor do ano 0, base qdd-plurianual (R$ 648.218,00) diferente da base ações-planejamento (R$ 1.048.218,00). Diferença de R$ -4e+05.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.096,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>A uo 2421, programa 124, ação 4516, função 20, subfunção 608 está com valor do ano 0, base qdd-plurianual (R$ 411.620,00) diferente da base ações-planejamento (R$ 3.911.620,00). Diferença de R$ -3500000.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.281.139.704,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>A uo 3041, programa 90, ação 4235, função 20, subfunção 606 está com valor do ano 0, base qdd-plurianual (R$ 92.806.224,00) diferente da base ações-planejamento (R$ 95.106.224,00). Diferença de R$ -2300000.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.781.144,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>A uo 3041, programa 97, ação 4236, função 20, subfunção 608 está com valor do ano 0, base qdd-plurianual (R$ 58.536.458,00) diferente da base ações-planejamento (R$ 78.162.208,00). Diferença de R$ -19625750.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>A uo 3041, programa 705, ação 2500, função 20, subfunção 122 está com valor do ano 0, base qdd-plurianual (R$ 1.744.815,00) diferente da base ações-planejamento (R$ 2.244.815,00). Diferença de R$ -5e+05.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 403,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>A uo 3051, programa 16, ação 4018, função 19, subfunção 571 está com valor do ano 0, base qdd-plurianual (R$ 31.454.979,00) diferente da base ações-planejamento (R$ 31.564.979,00). Diferença de R$ -110000.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.214.845,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>A uo 4251, programa 71, ação 2074, função 8, subfunção 244 está com valor do ano 0, base qdd-plurianual (R$ 213.000,00) diferente da base ações-planejamento (R$ 1.213.000,00). Diferença de R$ -1e+06.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 153.615.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>A uo 4491, programa 102, ação 4360, função 13, subfunção 392 está com valor do ano 0, base qdd-plurianual (R$ 31.999.000,00) diferente da base ações-planejamento (R$ 32.999.000,00). Diferença de R$ -1e+06.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.753.348.828,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.688.408.156,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 168.463.064,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 272.691.800,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 915.599.548,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 223.316.200,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 151.975,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.649.958,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.188.933,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.701.965,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 320.527.163,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.958.873,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.898.989,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 398.179.854,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 237.937.140,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 799.235,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 117.707.817,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 117.707.817,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.020.514,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 42.107.102,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.115.629,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 45.737.536,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 167.132.860,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.617.358,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 44.891.938,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.009.166,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.728.583,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.041.017,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.969.655,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.903.222,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 549.400,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.006.127,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.710.639,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 258.233,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.552.678,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 35.706,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 179.618,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.369.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.131.497.880,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 65.903.150,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 190.954.071,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.232.623,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.733.261,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.983.569,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.163.508,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 800.632.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 179.189.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 96.885.840,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.338.744.082,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.116.144.456,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 344.522.769,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.437.117,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 557.448.522,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.768.850,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 61.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.991.404,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.248.004,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.955.529,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.654.911,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.592.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.275.957,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 45.731.747,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.186.184,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.890.827,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 306.732,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.700.001,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.853.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 810.354,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 49.082.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.843.508.421,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.866.814,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.273.721,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 206.379.411,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 570.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 750.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 384.076.895,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.466.172,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.307.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.733.340,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 27.470.840,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.866.720,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.596.129.743,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.450.010.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 31.623.085,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 324.198.140,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.043.669,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 21.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.255.319,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.119.959,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.794.089,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.523.797,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.478.014,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.823.165,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.378.117,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.776.835,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.306.553,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.179.356,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.046.766,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.672,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.346.102,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 173.862.721,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.751.135,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.925.292,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.545.899,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 599.965,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>A uo 1911 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 987.555.711,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>A uo 1911 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 881.718,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>A uo 1915 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 935.539.611,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.906.514.319,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.463.855.475,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 500.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.473.853.111,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>A uo 1941 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 200.686.029,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>A uo 1941 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.585.571,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.259.699,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.740.045,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.009.139,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 62.536.715,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 301.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>A uo 1991 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.204.268.408,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 128.011.416,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 323.013.900,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.900.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.880.729,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.344.819,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 256.577.607,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 38.214.165,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.360.306.244,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.296.266,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 83.389.802,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.238.464,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.073.830,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.576.013,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.827.169,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 357.798,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.838.719,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 531.421,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.982.608,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.137.093,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.413.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.212.857,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 418.440.724,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.249.188,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.354.650,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.214.904,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 88.564.087,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 22.192.827,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 162.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 21.811.537,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 827.373,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 24.604.103,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.650.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.539.918,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.920.769,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.040,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 115.202.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.565.024,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.486.089,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.016.160,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.937.453,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.110.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 76.300.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.124.671,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.550.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 185.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.506.291.067,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.020.009.654,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.953.979,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 843.148.141,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 111.034.767,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.174.240,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 233.628.935,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.750.066,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.642.001,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 575.076,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 38.297.180,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.321.284,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.287.659,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 252.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.574.933,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.734.320,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.169.136,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 728.460,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.104.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.915.824,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.957.565,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 737.740,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.157.902,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 368.237,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.795.195,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.203.352,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.709.975,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.560.605,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 181.431,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.372.954,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.730.976,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.072,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.996.021,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.874.050,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.964.700,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.299.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 124.320,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.910.355,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 215.544,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 202.814.436,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.923.126,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.417.260,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.774.713,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.918.894,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 695.757,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.409.491,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.910.448,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.109.187,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 113.153.771,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.891.984,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 469.274.159,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.532.519,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 62.726.162,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.953,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.565.016.946,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.586.698,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 864.139.654,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 217.562.824,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 955.013,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.148.881,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.860.346,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.252.003,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.641.774,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 395.184,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.839,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 155.128.183,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.621.537,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 101.089.054,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.367.717,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 273.360.189,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.568.053,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.487.492,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 81.999.737,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.804.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 235.101.900,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 103.295.958,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.343.915,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 515.552.603,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 300.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 87.290.065,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 136.182.023,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.109.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 382.209.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.796.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.875.495,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.921.716,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.205.865,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 95.625,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 47.472.693,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.685.448,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.285.383,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 183.302.411,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 802.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.328.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 202.351.447,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.607.522,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.648.557,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.942.185,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 129.755,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.771.991,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.518.126,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 37.943,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 308.888.846,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.833.754,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.331.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 149.477.910,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 52.710,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 42.084.488,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 116.783,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.929.081,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 83.844,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 192.224.643,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.636.871,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.362.948,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.818.064,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.802.401,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.054.444,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 180.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.311.374,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.974.160,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.064.226,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.329.008,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.777.510,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.129.311,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.221.046,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 628.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.404.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 70.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.747.481,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 154.041,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.539.065,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.076.290,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.735.187,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.797.080,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 309.669,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.794.482,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.641.211,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.485.090,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.154.681,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 74.353.681,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.065.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 267.732.675,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 130.521.213,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.126.200,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 241.256.573,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.943.740,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.036.014,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 36.428.634,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 462.961,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.965.986,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 165.665,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 134.115.581,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.064.504,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.900.609,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.112.166,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.393.441,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 209.706,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>A uo 4101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.001.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>A uo 4101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.823.595,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>A uo 4111 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>A uo 4151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 176.020.630,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.583.449,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.118.889,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 424.208.015,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 78.574,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.035.293.623,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.969.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.774.705,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.638.885,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.819.950,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 75.291.774,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.156.206.562,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.128.988,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.317.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>A uo 4321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>A uo 4331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.568.459,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>A uo 4331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.568.459,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>A uo 4341 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 36.798.404,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>A uo 4341 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.031.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.229.918,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.535.553,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.415.671,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 218.908.438,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 44.477.455,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 86.477.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 298.527.033,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 260.023.437,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.336.412,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 322.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>A uo 4641 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>A uo 4661 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>A uo 4671 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>A uo 4701 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.050.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.384.509.986,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.952.878.323,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.976.443.576,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.247.405.731,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 500.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 330.736,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.912.016,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>A uo 4721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>A uo 4751 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.632.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>A uo 4751 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.367.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>A uo 4761 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.834.338,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>O programa 98 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>O programa 704 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>O programa 706 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>O programa 726 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>O programa 729 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>O programa 734 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>O programa 738 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>O programa 746 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>O programa 760 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>O programa 764 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>O programa 765 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>O programa 766 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>O programa 767 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>check_ods_exists</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>O programa 126 está sem objetivo de desenvolvimento estratégico definido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>check_ods_exists</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>O programa 138 está sem objetivo de desenvolvimento estratégico definido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>A uo 1251, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 263.715.306,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>A uo 1251, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 5.358.422,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 1.072.922.038,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 46.826.403,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>A uo 1451, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 910.719,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>A uo 1511, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 217.067.440,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>A uo 1511, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 26.828.521,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>A uo 1301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>A uo 1917 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (FAZENDA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>A uo 2301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>A uo 2431 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>A uo 2461 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>A uo 2471 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>A uo 2481 está com setor divergente na base ações-planejamento (PLANEJAMENTO E GESTÃO) em relação à tabela auxiliar setor-governo da loa (NA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>A uo 2781 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (PLANEJAMENTO E GESTÃO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>A uo 4171 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (AGRICULTURA, PECUÁRIA E ABASTECIMENTO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>A uo 4331 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>A uo 4381 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>A uo 4531 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (DESENVOLVIMENTO ECONÔMICO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>A uo 4631 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>A uo 4641 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>A uo 5261 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>A uo 2311, 
+programa 7, 
+área temática 03AT03 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 216.248.265,00) diferente da base ações-planejamento (R$ 151.136.947,00). Diferença de R$ -65111318.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>A uo 1191, 
+programa 20, 
+área temática 01AT01 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 13.239.000,00) diferente da base ações-planejamento (R$ 13.238.000,00). Diferença de R$ -1000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>A uo 1371, 
+programa 21, 
+área temática 11AT11 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 3.418.369.851,00) diferente da base ações-planejamento (R$ 115.369.851,00). Diferença de R$ -3.303e+09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>A uo 2151, 
+programa 42, 
+área temática 03AT03 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 31.775.244,00) diferente da base ações-planejamento (R$ 31.765.244,00). Diferença de R$ -10000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>A uo 4291, 
+programa 60, 
+área temática 04AT04 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 702.771.556,00) diferente da base ações-planejamento (R$ 702.247.087,00). Diferença de R$ -524469.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>A uo 1481, 
+programa 68, 
+área temática 10AT10 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 40.387.963,00) diferente da base ações-planejamento (R$ 27.201.811,00). Diferença de R$ -13186152.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>A uo 1481, 
+programa 83, 
+área temática 10AT10 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 1.562.570,00) diferente da base ações-planejamento (R$ 1.233.792,00). Diferença de R$ -328778.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>A uo 1301, 
+programa 99, 
+área temática 05AT05 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 37.444.335,00) diferente da base ações-planejamento (R$ 36.529.088,00). Diferença de R$ -915247.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>A uo 1491, 
+programa 119, 
+área temática 12AT12 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 35.963.734,00) diferente da base ações-planejamento (R$ 35.962.734,00). Diferença de R$ -1000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>A uo 1221, 
+programa 133, 
+área temática 02AT02 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 498.121.008,00) diferente da base ações-planejamento (R$ 495.758.569,00). Diferença de R$ -2362439.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>A uo 1251, 
+programa 136, 
+área temática 03AT03 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 257.268.346,00) diferente da base ações-planejamento (R$ 257.267.346,00). Diferença de R$ -1000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>A uo 1071, 
+programa 139, 
+área temática 12AT12 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 207.973.317,00) diferente da base ações-planejamento (R$ 207.973.316,00). Diferença de R$ -1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>A uo 2481, 
+programa 161, 
+área temática 08AT08 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 406.412.088,00) diferente da base ações-planejamento (R$ 406.411.088,00). Diferença de R$ -1000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>A uo 1261, 
+programa 165, 
+área temática 03AT03 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 44.615.293,00) diferente da base ações-planejamento (R$ 43.575.293,00). Diferença de R$ -1040000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>A uo 1501, 
+programa 705, 
+área temática 08AT08 está com valor 
+de meta orçamentária do ano 0, base programas (R$ 72.198.856.106,00) diferente da base ações-planejamento (R$ 72.198.854.106,00). Diferença de R$ -2000.</t>
         </is>
       </c>
     </row>
@@ -2630,7 +8414,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2648,121 +8432,201 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>check_count_acoes_is_deleted</t>
+          <t>check_composite_primary_key_indicadores</t>
         </is>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_count_programas_is_deleted</t>
         </is>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_count_acoes_is_deleted</t>
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
         </is>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>check_indicadores_indice_referencia_data_futura</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B10">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>check_ods_exists</t>
+          <t>check_indicadores_justificativa_previsao_em_apuracao</t>
         </is>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>check_setor_governo</t>
+          <t>check_indicadores_previsoes_exists</t>
         </is>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>check_valores_qdd_plurianual</t>
+          <t>check_indicadores_previsoes_zeradas</t>
         </is>
       </c>
       <c r="B13">
-        <v>88</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>check_intra_despesa</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>check_intra_detalhamento</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>check_limite_ano0</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>check_objetivos_estrategicos_exists</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>check_ods_exists</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>check_repasse_recursos</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>check_setor_governo</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>check_valores_sigplan_programas</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/checks-planejamento.xlsx
+++ b/data/checks-planejamento.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B667"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A ação 2060, na uo 1251, funcional-programática 10.302.135, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 4.257.085,00 na detalhamento de obras.</t>
+          <t>A ação 4268, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 10.000.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
@@ -498,1039 +498,1039 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A ação 1037, na uo 1301, funcional-programática 15.451.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 27.633.026,00 na detalhamento de obras.</t>
+          <t>A ação 4275, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 56.282.273,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A ação 1038, na uo 1301, funcional-programática 15.451.099, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 2.062.697,00 na detalhamento de obras.</t>
+          <t>A ação 4268, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 261.721.140,00 na qdd-fiscal e R$ 271.721.140,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A ação 1039, na uo 1301, funcional-programática 15.451.139, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 4.865.499,00 na detalhamento de obras.</t>
+          <t>A ação 4275, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 361.913.350,00 na qdd-fiscal e R$ 418.195.623,00 na detalhamento de obras.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A ação 1041, na uo 1301, funcional-programática 15.451.139, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 6.479.795,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 10 está com os valores totais de receita e despesa diferentes nas bases. R$ 86.813.437.501,00 na base orçamento fiscal da receita, e 91.514.592.757,00 na qdd fiscal. A diferença é de R$ -4701155256.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A ação 4441, na uo 1451, funcional-programática 06.243.146, iag 1, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 29.000.001,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 12 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.000,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 1000.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A ação 1048, na uo 1451, funcional-programática 06.421.130, iag 1, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 904.245,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 20 está com os valores totais de receita e despesa diferentes nas bases. R$ 0,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A ação 4063, na uo 1511, funcional-programática 06.181.032, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 150.000,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 31 está com os valores totais de receita e despesa diferentes nas bases. R$ 87.761.794,00 na base orçamento fiscal da receita, e 65.836.031,00 na qdd fiscal. A diferença é de R$ 21925763.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A ação 4058, na uo 2101, funcional-programática 18.541.031, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 350.000,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 40 está com os valores totais de receita e despesa diferentes nas bases. R$ 203.859,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 203859.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A ação 4059, na uo 2101, funcional-programática 18.541.031, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 1.000.000,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 46 está com os valores totais de receita e despesa diferentes nas bases. R$ 2.901,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 2901.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A ação 4268, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 10.000.000,00 na qdd-fiscal e R$ 251.721.140,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 47 está com os valores totais de receita e despesa diferentes nas bases. R$ 35.242.116,00 na base orçamento fiscal da receita, e 31.436.436,00 na qdd fiscal. A diferença é de R$ 3805680.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A ação 4272, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 49.194.754,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 48 está com os valores totais de receita e despesa diferentes nas bases. R$ 327.327.763,00 na base orçamento fiscal da receita, e 7.207.328.033,00 na qdd fiscal. A diferença é de R$ -6880000270.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A ação 4275, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 56.282.273,00 na qdd-fiscal e R$ 251.008.739,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 52 está com os valores totais de receita e despesa diferentes nas bases. R$ 55.754.000,00 na base orçamento fiscal da receita, e 23.650.000,00 na qdd fiscal. A diferença é de R$ 32104000.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A ação 4287, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 1.000,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 53 está com os valores totais de receita e despesa diferentes nas bases. R$ 2.000,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 2000.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A ação 4289, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 1.000,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 59 está com os valores totais de receita e despesa diferentes nas bases. R$ 455.621.137,00 na base orçamento fiscal da receita, e 388.170.423,00 na qdd fiscal. A diferença é de R$ 67450714.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A ação 4293, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 690.658.203,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 60 está com os valores totais de receita e despesa diferentes nas bases. R$ 4.506.993.690,00 na base orçamento fiscal da receita, e 5.326.603.517,00 na qdd fiscal. A diferença é de R$ -819609827.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A ação 4385, na uo 2301, funcional-programática 26.782.081, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 32.000.000,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 61 está com os valores totais de receita e despesa diferentes nas bases. R$ 510.759.469,00 na base orçamento fiscal da receita, e 454.124.918,00 na qdd fiscal. A diferença é de R$ 56634551.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A ação 4280, na uo 2301, funcional-programática 26.782.139, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 9.000.000,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 72 está com os valores totais de receita e despesa diferentes nas bases. R$ 470.959.523,00 na base orçamento fiscal da receita, e 378.466.043,00 na qdd fiscal. A diferença é de R$ 92493480.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A ação 4238, na uo 2371, funcional-programática 20.609.078, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 8.311.374,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 79 está com os valores totais de receita e despesa diferentes nas bases. R$ 16.160.491,00 na base orçamento fiscal da receita, e 3.369.600,00 na qdd fiscal. A diferença é de R$ 12790891.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_tesouro</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A ação 1016, na uo 2421, funcional-programática 08.544.101, iag 0, está com valores do Tesouro diferentes entre as bases, R$ 0,00 na qdd-fiscal e R$ 477.508,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 80 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.019.599.103,00 na base orçamento fiscal da receita, e 778.721.696,00 na qdd fiscal. A diferença é de R$ 240877407.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A ação 2060, na UO 1251, funcional-programática 10.302.135 iag 0, está com valores diferentes entre as bases, R$ 4.257.085,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 91 está com os valores totais de receita e despesa diferentes nas bases. R$ 149.914.755,00 na base orçamento fiscal da receita, e 95.820.233,00 na qdd fiscal. A diferença é de R$ 54094522.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A ação 1037, na UO 1301, funcional-programática 15.451.081 iag 0, está com valores diferentes entre as bases, R$ 158.935.952,00 na qdd-fiscal e R$ 131.302.926,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 94 está com os valores totais de receita e despesa diferentes nas bases. R$ 10.873.232,00 na base orçamento fiscal da receita, e 7.321.724,00 na qdd fiscal. A diferença é de R$ 3551508.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_fechamento_fonte_orcam_fiscal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A ação 1038, na UO 1301, funcional-programática 15.451.099 iag 0, está com valores diferentes entre as bases, R$ 5.332.352,00 na qdd-fiscal e R$ 3.269.655,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 95 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.312.851.799,00 na base orçamento fiscal da receita, e 750.000,00 na qdd fiscal. A diferença é de R$ 1312101799.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A ação 1039, na UO 1301, funcional-programática 15.451.139 iag 0, está com valores diferentes entre as bases, R$ 4.865.499,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso NA está com os valores totais de receita e despesa diferentes nas bases. R$ 9.290.788.295,00 na base receita de investimento, e R$  NA na qdd investimento. A diferença é de R$ 9290788295.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A ação 1041, na UO 1301, funcional-programática 15.451.139 iag 0, está com valores diferentes entre as bases, R$ 9.208.378,00 na qdd-fiscal e R$ 2.728.583,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 11101 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 4.000,00 na qdd investimento. A diferença é de R$ 4000.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A ação 4441, na UO 1451, funcional-programática 06.243.146 iag 1, está com valores diferentes entre as bases, R$ 29.000.001,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 12400 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 1.123.941.920,00 na qdd investimento. A diferença é de R$ 1123941920.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_fechamento_fonte_orcam_investimento</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A ação 1048, na UO 1451, funcional-programática 06.421.130 iag 1, está com valores diferentes entre as bases, R$ 45.212.295,00 na qdd-fiscal e R$ 44.308.050,00 na detalhamento de obras.</t>
+          <t>A Fonte de Recurso 51000 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 8.166.842.375,00 na qdd investimento. A diferença é de R$ 8166842375.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A ação 4063, na UO 1511, funcional-programática 06.181.032 iag 0, está com valores diferentes entre as bases, R$ 20.000.000,00 na qdd-fiscal e R$ 19.850.000,00 na detalhamento de obras.</t>
+          <t>O programa 165 contém indicador (IDEB ANOS INICIAIS...) que, apesar de ter índice de referência de 63, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A ação 4058, na UO 2101, funcional-programática 18.541.031 iag 0, está com valores diferentes entre as bases, R$ 350.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 165 contém indicador (IDEB ANOS FINAIS...) que, apesar de ter índice de referência de 46, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A ação 4059, na UO 2101, funcional-programática 18.541.031 iag 0, está com valores diferentes entre as bases, R$ 1.000.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 165 contém indicador (IDEB ENSINO MÉDIO...) que, apesar de ter índice de referência de 4, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A ação 4268, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 261.721.140,00 na qdd-fiscal e R$ 20.000.000,00 na detalhamento de obras.</t>
+          <t>O programa 167 contém indicador (IDEB ANOS INICIAIS...) que, apesar de ter índice de referência de 63, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A ação 4272, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 49.194.754,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 167 contém indicador (IDEB ENSINO MÉDIO...) que, apesar de ter índice de referência de 4, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A ação 4275, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 361.913.350,00 na qdd-fiscal e R$ 167.186.884,00 na detalhamento de obras.</t>
+          <t>O programa 167 contém indicador (IDEB ANOS FINAIS...) que, apesar de ter índice de referência de 46, está sem meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A ação 4287, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 1.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 3 contém indicador (ÍNDICE DE EFETIVIDADE...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A ação 4289, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 1.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 36 contém indicador (Unidade de identidade...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A ação 4293, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 777.948.268,00 na qdd-fiscal e R$ 87.290.065,00 na detalhamento de obras.</t>
+          <t>O programa 91 contém indicador (DISCENTES FORMADOS E...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A ação 4385, na UO 2301, funcional-programática 26.782.081 iag 0, está com valores diferentes entre as bases, R$ 32.000.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 91 contém indicador (GRAU DE SATISFAÇÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A ação 4280, na UO 2301, funcional-programática 26.782.139 iag 0, está com valores diferentes entre as bases, R$ 9.000.000,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 91 contém indicador (ARTIGOS ACADÊMICOS ACEITOS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A ação 4238, na UO 2371, funcional-programática 20.609.078 iag 0, está com valores diferentes entre as bases, R$ 8.311.374,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>O programa 160 contém indicador (EFICÁCIA DA GESTÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>check_detalhamento_obras_orcam_fiscal_outros</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A ação 1016, na UO 2421, funcional-programática 08.544.101 iag 0, está com valores diferentes entre as bases, R$ 477.508,00 na qdd-fiscal e R$ 0,00 na detalhamento de obras.</t>
+          <t>A uo 2011 está com valor recebido de recursos intraorçamentários (R$ 617.928.493,00) diferente do valor detalhado (R$ 1.258.925.701,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 10 está com os valores totais de receita e despesa diferentes nas bases. R$ 86.813.437.501,00 na base orçamento fiscal da receita, e 91.514.592.757,00 na qdd fiscal. A diferença é de R$ -4701155256.</t>
+          <t>A uo 2121 está com valor recebido de recursos intraorçamentários (R$ 2.440.013.976,00) diferente do valor detalhado (R$ 2.651.552.847,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 12 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.000,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 1000.</t>
+          <t>A uo 2261 está com valor recebido de recursos intraorçamentários (R$ 662.950.136,00) diferente do valor detalhado (R$ 668.915.291,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 20 está com os valores totais de receita e despesa diferentes nas bases. R$ 0,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ NA.</t>
+          <t>A uo 2321 está com valor recebido de recursos intraorçamentários (R$ 494.081.184,00) diferente do valor detalhado (R$ 496.238.756,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 31 está com os valores totais de receita e despesa diferentes nas bases. R$ 87.761.794,00 na base orçamento fiscal da receita, e 65.836.031,00 na qdd fiscal. A diferença é de R$ 21925763.</t>
+          <t>A uo 2361 está com valor recebido de recursos intraorçamentários (R$ 15.037.000,00) diferente do valor detalhado (R$ 135.037.000,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 40 está com os valores totais de receita e despesa diferentes nas bases. R$ 203.859,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 203859.</t>
+          <t>A uo 4711 está com valor recebido de recursos intraorçamentários (R$ 7.976.441.576,00) diferente do valor detalhado (R$ 6.559.015.073,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 46 está com os valores totais de receita e despesa diferentes nas bases. R$ 2.901,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 2901.</t>
+          <t>A uo 9901 está com valor recebido de recursos intraorçamentários (R$ 648.487.316,00) diferente do valor detalhado (R$ 941.204.042,00) na base intra-detalhamento.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 47 está com os valores totais de receita e despesa diferentes nas bases. R$ 35.242.116,00 na base orçamento fiscal da receita, e 31.436.436,00 na qdd fiscal. A diferença é de R$ 3805680.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.287.437.285,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 48 está com os valores totais de receita e despesa diferentes nas bases. R$ 327.327.763,00 na base orçamento fiscal da receita, e 7.207.328.033,00 na qdd fiscal. A diferença é de R$ -6880000270.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 354.200.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 52 está com os valores totais de receita e despesa diferentes nas bases. R$ 55.754.000,00 na base orçamento fiscal da receita, e 23.650.000,00 na qdd fiscal. A diferença é de R$ 32104000.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 53 está com os valores totais de receita e despesa diferentes nas bases. R$ 2.000,00 na base orçamento fiscal da receita, e  NA na qdd fiscal. A diferença é de R$ 2000.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 344.471.800,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 59 está com os valores totais de receita e despesa diferentes nas bases. R$ 455.621.137,00 na base orçamento fiscal da receita, e 388.170.423,00 na qdd fiscal. A diferença é de R$ 67450714.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 135.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 60 está com os valores totais de receita e despesa diferentes nas bases. R$ 4.506.993.690,00 na base orçamento fiscal da receita, e 5.326.603.517,00 na qdd fiscal. A diferença é de R$ -819609827.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 30.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 61 está com os valores totais de receita e despesa diferentes nas bases. R$ 510.759.469,00 na base orçamento fiscal da receita, e 454.124.918,00 na qdd fiscal. A diferença é de R$ 56634551.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 72 está com os valores totais de receita e despesa diferentes nas bases. R$ 470.959.523,00 na base orçamento fiscal da receita, e 378.466.043,00 na qdd fiscal. A diferença é de R$ 92493480.</t>
+          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.953.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 79 está com os valores totais de receita e despesa diferentes nas bases. R$ 16.160.491,00 na base orçamento fiscal da receita, e 3.369.600,00 na qdd fiscal. A diferença é de R$ 12790891.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 714.778.494,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 80 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.019.599.103,00 na base orçamento fiscal da receita, e 778.721.696,00 na qdd fiscal. A diferença é de R$ 240877407.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 319.899.495,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 91 está com os valores totais de receita e despesa diferentes nas bases. R$ 149.914.755,00 na base orçamento fiscal da receita, e 95.820.233,00 na qdd fiscal. A diferença é de R$ 54094522.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 161.811.560,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 94 está com os valores totais de receita e despesa diferentes nas bases. R$ 10.873.232,00 na base orçamento fiscal da receita, e 7.321.724,00 na qdd fiscal. A diferença é de R$ 3551508.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 95.102.996,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_fiscal</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 95 está com os valores totais de receita e despesa diferentes nas bases. R$ 1.312.851.799,00 na base orçamento fiscal da receita, e 750.000,00 na qdd fiscal. A diferença é de R$ 1312101799.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_investimento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso NA está com os valores totais de receita e despesa diferentes nas bases. R$ 9.290.788.295,00 na base receita de investimento, e R$  NA na qdd investimento. A diferença é de R$ 9290788295.</t>
+          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.752.235,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_investimento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 11101 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 4.000,00 na qdd investimento. A diferença é de R$ 4000.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.846.022.621,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_investimento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 12400 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 1.123.941.920,00 na qdd investimento. A diferença é de R$ 1123941920.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.073.299.042,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>check_fechamento_fonte_orcam_investimento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 51000 está com os valores totais de receita e despesa diferentes nas bases. R$  NA na base receita de investimento, e R$ 8.166.842.375,00 na qdd investimento. A diferença é de R$ 8166842375.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>O programa 6 contém indicador (GASTO PER CAPITA...) que, apesar de ter índice de referência de 384524, está sem meta para o ano 3.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 908.022.281,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>O programa 165 contém indicador (IDEB ANOS INICIAIS...) que, apesar de ter índice de referência de 63, está sem meta para o ano 3.</t>
+          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 399.038.512,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>O programa 165 contém indicador (IDEB ANOS FINAIS...) que, apesar de ter índice de referência de 46, está sem meta para o ano 3.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 115.458.254,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>O programa 165 contém indicador (IDEB ENSINO MÉDIO...) que, apesar de ter índice de referência de 4, está sem meta para o ano 3.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.303.609,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>O programa 167 contém indicador (IDEB ANOS INICIAIS...) que, apesar de ter índice de referência de 63, está sem meta para o ano 3.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>O programa 167 contém indicador (IDEB ENSINO MÉDIO...) que, apesar de ter índice de referência de 4, está sem meta para o ano 3.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.324.521,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>O programa 167 contém indicador (IDEB ANOS FINAIS...) que, apesar de ter índice de referência de 46, está sem meta para o ano 3.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.064.254,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>O programa 3 contém indicador (ÍNDICE DE EFETIVIDADE...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.097.663,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>O programa 36 contém indicador (Unidade de identidade...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>O programa 91 contém indicador (DISCENTES FORMADOS E...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.628.259,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>O programa 91 contém indicador (GRAU DE SATISFAÇÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.609.120,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>O programa 91 contém indicador (ARTIGOS ACADÊMICOS ACEITOS...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>check_indicadores_consistency_indice_de_referencia_missing</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>O programa 160 contém indicador (EFICÁCIA DA GESTÃO...) que, apesar não de ter índice de referência, está com meta para o ano 3.</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.580.735,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>check_indicadores_justificativa_previsao_em_apuracao</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>O programa 6 contém indicador (GASTO PER CAPITA...) que, apesar de estar sem previsão para o ano 3, apresenta justificativa de previsão inválida, com menos de 50 caracteres (0 caract.).</t>
+          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 87.750,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>O programa 6 contém indicador (GASTO PER CAPITA...) cuja previsão, apesar de não estar em apuração, está sem valor para o ano 3.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 395.202.978,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>O programa 6 contém indicador (GASTO PER CAPITA...) cuja previsão, apesar de não estar em apuração, está com valor zerado para o ano 3.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 658.905.647,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>check_intra_despesa</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A uo 1271, na ação 2417, grupo 1, elemento-item 1321, possui inconsistência nos valores da despesa intraorçamentária (modalidade 91) da base despesa-item fiscal (R$ 272.259,00) e da base intra-repasse (R$ 230.431,00).</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.516.568,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>check_intra_despesa</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A uo 1271, na ação 2417, grupo 1, elemento-item 1326, possui inconsistência nos valores da despesa intraorçamentária (modalidade 91) da base despesa-item fiscal (R$ 2.672.505,00) e da base intra-repasse (R$ 2.714.333,00).</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.676.685,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A uo 2011 está com valor recebido de recursos intraorçamentários (R$ 617.928.493,00) diferente do valor detalhado (R$ 1.258.967.529,00) na base intra-detalhamento.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 224.961.893,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A uo 2121 está com valor recebido de recursos intraorçamentários (R$ 2.440.013.976,00) diferente do valor detalhado (R$ 2.651.552.847,00) na base intra-detalhamento.</t>
+          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.697.432,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A uo 2261 está com valor recebido de recursos intraorçamentários (R$ 662.950.136,00) diferente do valor detalhado (R$ 668.915.291,00) na base intra-detalhamento.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.042.666.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A uo 2321 está com valor recebido de recursos intraorçamentários (R$ 494.081.184,00) diferente do valor detalhado (R$ 496.238.756,00) na base intra-detalhamento.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 111.710.700,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A uo 2361 está com valor recebido de recursos intraorçamentários (R$ 15.037.000,00) diferente do valor detalhado (R$ 135.037.000,00) na base intra-detalhamento.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>A uo 4711 está com valor recebido de recursos intraorçamentários (R$ 7.976.441.576,00) diferente do valor detalhado (R$ 6.558.973.245,00) na base intra-detalhamento.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 459.800.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>A uo 9901 está com valor recebido de recursos intraorçamentários (R$ 648.487.316,00) diferente do valor detalhado (R$ 941.204.042,00) na base intra-detalhamento.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 338.713.676,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.287.437.285,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.336.775,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 354.200.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.663.225,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 344.471.800,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.016.356,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 135.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.236.596,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 30.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.801.362,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.629.148.025,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A uo 1011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.953.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 314.144.747,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 714.778.494,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 82.434.724,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 319.899.495,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.800.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 161.811.560,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.874.808,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 95.102.996,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.173.695,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.408.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A uo 1021 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.752.235,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 24.696.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.846.022.621,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.447.984,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.073.299.042,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 884.409,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.962.078,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 908.022.281,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.195.653,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>A uo 1031 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 399.038.512,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 566.797,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 115.458.254,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.006.091,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.303.609,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.604.258,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 320.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.324.521,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.666.912,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.064.254,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.097.663,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 78.921.382,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>A uo 1051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 22.274.854,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.628.259,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.893.562,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.609.120,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.337.677,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.580.735,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.458.016,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>A uo 1071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 87.750,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.524.705,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 395.202.978,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.228.611,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 658.905.647,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.823.948,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.516.568,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 307.035,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.676.685,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.251.732,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 224.961.893,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.327.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>A uo 1081 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.697.432,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.426.625.358,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.042.666.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 128.236.192,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 111.710.700,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 204.135.476,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 648.489.316,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 459.800.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.609.779,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 338.713.676,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.096,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.336.775,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.281.139.704,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.663.225,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.781.144,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>A uo 1091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.016.356,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 403,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.236.596,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.214.845,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>A uo 1101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.801.362,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 153.615.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.629.148.025,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.753.348.828,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 314.144.747,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.688.408.156,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 82.434.724,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 168.463.064,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.800.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 272.691.800,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.874.808,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 915.599.548,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.173.695,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 223.316.200,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>A uo 1191 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.408.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 151.975,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 24.696.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.649.958,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.447.984,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.188.933,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 884.409,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.701.965,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.962.078,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 320.527.163,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.195.653,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.958.873,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 566.797,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.898.989,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.006.091,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.604.258,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 398.179.854,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 320.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 237.937.140,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.666.912,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 799.235,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>A uo 1221 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 78.921.382,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 117.707.817,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 22.274.854,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 117.707.817,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.893.562,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.337.677,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.020.514,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 42.107.102,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.458.016,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.524.705,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.115.629,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.228.611,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 45.737.536,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.823.948,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 167.132.860,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 307.035,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.251.732,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.617.358,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>A uo 1231 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.327.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 44.891.938,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.426.625.358,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.009.166,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 128.236.192,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.728.583,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 204.135.476,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.041.017,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 648.489.316,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.969.655,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.609.779,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.903.222,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.096,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 549.400,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.281.139.704,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.006.127,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.781.144,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.710.639,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 258.233,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 403,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>A uo 1251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.214.845,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.552.678,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 153.615.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 35.706,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.753.348.828,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 179.618,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.688.408.156,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.369.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 168.463.064,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 272.691.800,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.131.497.880,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 915.599.548,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 65.903.150,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 223.316.200,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 151.975,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 190.954.071,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.649.958,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.232.623,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.188.933,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.733.261,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.701.965,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.983.569,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 320.527.163,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.163.508,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.958.873,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 800.632.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.898.989,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 398.179.854,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 179.189.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 237.937.140,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 96.885.840,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 799.235,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.338.744.082,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 117.707.817,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.116.144.456,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 117.707.817,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>A uo 1261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 344.522.769,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.020.514,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.437.117,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 42.107.102,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 557.448.522,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.768.850,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>A uo 1271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.115.629,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 61.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 45.737.536,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.991.404,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 167.132.860,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.248.004,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.955.529,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.617.358,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.654.911,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 44.891.938,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.592.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.009.166,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.275.957,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.728.583,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 45.731.747,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.041.017,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.186.184,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>A uo 1301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.969.655,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.890.827,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.903.222,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 306.732,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 549.400,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.700.001,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.006.127,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.853.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.710.639,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 810.354,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 258.233,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 49.082.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.843.508.421,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.552.678,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.866.814,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 35.706,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.273.721,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 179.618,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 206.379.411,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.369.600,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 570.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>A uo 1371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 750.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.131.497.880,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 384.076.895,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 65.903.150,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.466.172,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.307.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 190.954.071,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.733.340,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.232.623,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 27.470.840,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.733.261,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.866.720,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.983.569,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.596.129.743,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>A uo 1401 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.163.508,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.450.010.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 800.632.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 31.623.085,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 324.198.140,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 179.189.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.043.669,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 96.885.840,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 21.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>A uo 1441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.255.319,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.338.744.082,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.119.959,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.116.144.456,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.794.089,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.523.797,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 344.522.769,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.478.014,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.437.117,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.823.165,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 557.448.522,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.378.117,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.768.850,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.776.835,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 61.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.306.553,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>A uo 1451 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.991.404,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.179.356,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.248.004,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.046.766,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.955.529,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.672,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.654.911,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.346.102,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.592.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 173.862.721,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.275.957,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.751.135,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 45.731.747,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.925.292,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.186.184,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.545.899,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.890.827,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 599.965,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 306.732,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.700.001,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1911 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 987.555.711,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.853.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1911 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 881.718,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>A uo 1481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 810.354,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1915 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 49.082.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 935.539.611,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.843.508.421,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.866.814,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>A uo 1491 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.273.721,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.906.514.319,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 206.379.411,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.463.855.475,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 570.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 500.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 750.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.473.853.111,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 384.076.895,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1941 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 200.686.029,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.466.172,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1941 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.585.571,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.307.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.259.699,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.733.340,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.740.045,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 27.470.840,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.009.139,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>A uo 1501 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.866.720,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 62.536.715,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.596.129.743,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 301.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.450.010.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1991 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.204.268.408,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 31.623.085,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 128.011.416,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 323.013.900,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 324.198.140,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.900.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.043.669,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.880.729,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>A uo 1511 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 21.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.344.819,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.255.319,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 256.577.607,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.119.959,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 38.214.165,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.794.089,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.360.306.244,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>A uo 1521 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.523.797,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.296.266,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.478.014,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.823.165,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 83.389.802,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.378.117,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.238.464,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>A uo 1541 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.776.835,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.073.830,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.306.553,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.576.013,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.179.356,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.046.766,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.827.169,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>A uo 1631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.672,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 357.798,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.346.102,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.838.719,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 173.862.721,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 531.421,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>A uo 1711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.751.135,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.982.608,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.925.292,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.137.093,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.545.899,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.413.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 599.965,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.212.857,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>A uo 1721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>A uo 1911 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 987.555.711,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 418.440.724,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>A uo 1911 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 881.718,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.249.188,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>A uo 1915 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.354.650,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 935.539.611,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.214.904,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 88.564.087,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 22.192.827,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.906.514.319,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 162.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.463.855.475,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 500.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 21.811.537,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>A uo 1916 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.473.853.111,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 827.373,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>A uo 1941 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 200.686.029,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 24.604.103,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>A uo 1941 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.585.571,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.650.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.259.699,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.539.918,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.740.045,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.920.769,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.009.139,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.040,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 62.536.715,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 115.202.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>A uo 1951 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 301.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.565.024,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>A uo 1991 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.204.268.408,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.486.089,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 128.011.416,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.016.160,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 323.013.900,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.937.453,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.900.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.110.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.880.729,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 76.300.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.344.819,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.124.671,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 256.577.607,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.550.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 38.214.165,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.360.306.244,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 185.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.296.266,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 83.389.802,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.506.291.067,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.238.464,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.020.009.654,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>A uo 2011 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.073.830,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.953.979,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.576.013,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 843.148.141,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 111.034.767,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.827.169,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.174.240,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>A uo 2041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 357.798,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 233.628.935,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.838.719,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.750.066,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 531.421,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.642.001,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.982.608,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 575.076,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.137.093,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 38.297.180,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>A uo 2061 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.413.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.212.857,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.321.284,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.287.659,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 418.440.724,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 252.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.249.188,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.574.933,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.354.650,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.734.320,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.214.904,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 88.564.087,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.169.136,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 22.192.827,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 728.460,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>A uo 2071 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 162.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.104.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.915.824,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 21.811.537,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 827.373,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.957.565,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 24.604.103,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 737.740,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.650.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.539.918,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.157.902,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.920.769,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 368.237,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>A uo 2091 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.040,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.795.195,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 115.202.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.203.352,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.565.024,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.709.975,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 19.486.089,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.560.605,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.016.160,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 181.431,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.937.453,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.372.954,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.110.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.730.976,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 76.300.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.072,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.124.671,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.996.021,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.550.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.874.050,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.964.700,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 185.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.299.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>A uo 2101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 124.320,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.506.291.067,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.910.355,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.020.009.654,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 215.544,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.953.979,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 202.814.436,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 843.148.141,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.923.126,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 111.034.767,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.417.260,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.174.240,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 233.628.935,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.774.713,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.750.066,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.918.894,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.642.001,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 695.757,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>A uo 2121 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 575.076,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.409.491,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 38.297.180,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.910.448,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.109.187,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.321.284,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 113.153.771,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.287.659,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 252.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.891.984,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>A uo 2151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.574.933,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 469.274.159,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.734.320,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.532.519,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 62.726.162,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.169.136,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.953,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 728.460,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.565.016.946,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>A uo 2161 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.104.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.586.698,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.915.824,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 864.139.654,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.957.565,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 217.562.824,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 737.740,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 955.013,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>A uo 2171 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.148.881,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.157.902,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.860.346,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 368.237,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.252.003,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.795.195,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.203.352,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.641.774,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>A uo 2181 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.709.975,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 395.184,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.560.605,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.839,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 181.431,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 155.128.183,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.372.954,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.621.537,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.730.976,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 101.089.054,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>A uo 2201 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.072,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.367.717,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.996.021,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 273.360.189,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.874.050,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.568.053,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.964.700,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.487.492,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.299.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 81.999.737,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>A uo 2211 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 124.320,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.804.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.910.355,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 235.101.900,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 215.544,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 103.295.958,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 202.814.436,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.343.915,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 13.923.126,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 515.552.603,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.417.260,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 300.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 87.290.065,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>A uo 2241 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.774.713,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 136.182.023,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 23.918.894,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.109.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 695.757,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 382.209.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.409.491,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.796.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.910.448,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.875.495,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>A uo 2251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.109.187,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.921.716,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 113.153.771,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.205.865,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 95.625,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.891.984,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 47.472.693,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 469.274.159,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.685.448,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.532.519,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.285.383,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 62.726.162,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>A uo 2261 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.953,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 183.302.411,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.565.016.946,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 802.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.586.698,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.328.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 32.002.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 202.351.447,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 864.139.654,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.607.522,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 217.562.824,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.648.557,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 955.013,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.148.881,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.942.185,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>A uo 2271 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 12.860.346,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 129.755,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.252.003,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.771.991,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.518.126,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.641.774,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 37.943,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 395.184,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>A uo 2281 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.839,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 308.888.846,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 155.128.183,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.833.754,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.621.537,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.331.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 101.089.054,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 149.477.910,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 41.367.717,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 52.710,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 273.360.189,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 42.084.488,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.568.053,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 116.783,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.487.492,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.929.081,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 81.999.737,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 83.844,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 192.224.643,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.804.861,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 235.101.900,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.636.871,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 103.295.958,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.362.948,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 43.343.915,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.818.064,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 515.552.603,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.802.401,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 300.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.054.444,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 87.290.065,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 136.182.023,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 180.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>A uo 2301 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 105.109.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.311.374,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 382.209.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.796.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.974.160,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.875.495,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.064.226,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.921.716,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.329.008,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 123.205.865,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.777.510,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 95.625,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.129.311,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 47.472.693,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.685.448,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.221.046,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.285.383,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 628.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>A uo 2311 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.100,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.404.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 183.302.411,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 70.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 802.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.747.481,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.328.417,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 154.041,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 202.351.447,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.539.065,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 29.607.522,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.076.290,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>A uo 2321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.648.557,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.735.187,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.942.185,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.797.080,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 129.755,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 309.669,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.771.991,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.794.482,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.518.126,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 37.943,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>A uo 2331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.100.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.641.211,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 308.888.846,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.833.754,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.485.090,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.331.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.154.681,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 149.477.910,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 52.710,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 74.353.681,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 42.084.488,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 116.783,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.065.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.929.081,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 267.732.675,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>A uo 2351 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 83.844,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 130.521.213,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 192.224.643,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.126.200,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 241.256.573,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 57.636.871,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.943.740,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.362.948,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.818.064,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.036.014,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.802.401,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 36.428.634,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.054.444,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 462.961,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.965.986,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 180.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>A uo 2371 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.311.374,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 165.665,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 134.115.581,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.974.160,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 15.064.226,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.064.504,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.329.008,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.900.609,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>A uo 2421 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.777.510,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.112.166,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.129.311,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.393.441,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.221.046,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 628.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.404.353,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 209.706,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>A uo 2431 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 70.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.001.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.747.481,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.823.595,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 154.041,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4111 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.539.065,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>A uo 2441 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.076.290,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 176.020.630,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.735.187,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.583.449,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.118.889,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.797.080,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 309.669,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 424.208.015,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.794.482,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 78.574,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.035.293.623,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>A uo 2461 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.969.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.641.211,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.774.705,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.638.885,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.485.090,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.819.950,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.154.681,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 75.291.774,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>A uo 2471 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.156.206.562,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 74.353.681,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.128.988,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.317.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.065.350,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 267.732.675,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.568.459,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 130.521.213,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.568.459,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>A uo 2481 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 8.126.200,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4341 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 36.798.404,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 241.256.573,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4341 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.031.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.943.740,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.229.918,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.535.553,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.036.014,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.415.671,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 36.428.634,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 218.908.438,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 462.961,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 44.477.455,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 59.965.986,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 86.477.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>A uo 3041 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 165.665,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 298.527.033,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 134.115.581,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 260.023.437,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.336.412,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.064.504,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 322.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>A uo 3051 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 26.900.609,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4641 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.112.166,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4661 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.393.441,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4671 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4701 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.050.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.384.509.986,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.500.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>A uo 3151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 209.706,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.952.878.323,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>A uo 4101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.001.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.976.443.576,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>A uo 4101 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 16.823.595,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.247.405.731,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>A uo 4111 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 500.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>A uo 4151 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 330.736,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 176.020.630,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.912.016,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 18.583.449,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 3.118.889,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>A uo 4251 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 20.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4751 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.632.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 424.208.015,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4751 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.367.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
@@ -7230,965 +7230,461 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 78.574,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4761 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.834.338,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 11.035.293.623,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 98 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.969.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 704 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.774.705,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 706 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.638.885,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 726 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 10.819.950,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 729 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 75.291.774,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 734 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.156.206.562,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 738 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 28.128.988,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 746 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>A uo 4291 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 14.317.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 760 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>A uo 4321 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 764 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>A uo 4331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.568.459,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 765 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>A uo 4331 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.568.459,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 766 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>A uo 4341 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 36.798.404,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 767 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_ods_exists</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>A uo 4341 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.031.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 126 está sem objetivo de desenvolvimento estratégico definido.</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_ods_exists</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 50.229.918,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>O programa 138 está sem objetivo de desenvolvimento estratégico definido.</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 6.535.553,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 263.715.306,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 5.415.671,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1251, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 5.358.422,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>A uo 4381 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 218.908.438,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 1.072.922.038,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 44.477.455,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 46.826.403,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 86.477.590,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1451, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 910.719,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>A uo 4551 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 250.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 217.067.440,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 298.527.033,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1511, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 26.828.521,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 260.023.437,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 17.336.412,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 1917 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (FAZENDA).</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>A uo 4631 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 322.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>A uo 4641 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2431 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>A uo 4661 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2461 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>A uo 4671 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2471 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>A uo 4701 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.050.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2481 está com setor divergente na base ações-planejamento (PLANEJAMENTO E GESTÃO) em relação à tabela auxiliar setor-governo da loa (NA).</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.384.509.986,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 2781 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (PLANEJAMENTO E GESTÃO).</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4171 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (AGRICULTURA, PECUÁRIA E ABASTECIMENTO).</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.952.878.323,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4331 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 7.976.443.576,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4381 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 4.247.405.731,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4531 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (DESENVOLVIMENTO ECONÔMICO).</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 500.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4631 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 330.736,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 4641 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 71.912.016,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
+          <t>A uo 5261 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_valores_sigplan_programas</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
-        <is>
-          <t>A uo 4711 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 25.000.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>check_limite_ano0</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>A uo 4721 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 1.000,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>check_limite_ano0</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>A uo 4751 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 9.632.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>check_limite_ano0</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>A uo 4751 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 2.367.500,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>check_limite_ano0</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>A uo 4761 está com uma diferença de R$  NA entre o valor de limite no ano 0 (R$ 51.834.338,00) e a soma do valor utilizado no ano (R$ NA) com o valor transferido no ano (R$ NA), que totalizam R$ NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>O programa 98 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>O programa 704 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>O programa 706 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>O programa 726 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>O programa 729 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>O programa 734 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>O programa 738 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>O programa 746 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>O programa 760 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>O programa 764 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>O programa 765 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>O programa 766 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>check_objetivos_estrategicos_exists</t>
-        </is>
-      </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>O programa 767 está sem objetivo estratégico válido na base programas-planejamento (3-Não há objetivo estratégico vinculado.). Cada programa precisa ter pelo menos um objetivo estratégico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>check_ods_exists</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>O programa 126 está sem objetivo de desenvolvimento estratégico definido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>check_ods_exists</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>O programa 138 está sem objetivo de desenvolvimento estratégico definido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>A uo 1251, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 263.715.306,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>A uo 1251, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 5.358.422,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 1.072.922.038,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 46.826.403,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>A uo 1451, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 910.719,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>A uo 1511, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 217.067.440,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>A uo 1511, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 26.828.521,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>A uo 1301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>A uo 1917 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (FAZENDA).</t>
-        </is>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>A uo 2301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>A uo 2431 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>A uo 2461 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>A uo 2471 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>A uo 2481 está com setor divergente na base ações-planejamento (PLANEJAMENTO E GESTÃO) em relação à tabela auxiliar setor-governo da loa (NA).</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>A uo 2781 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (PLANEJAMENTO E GESTÃO).</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>A uo 4171 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (AGRICULTURA, PECUÁRIA E ABASTECIMENTO).</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>A uo 4331 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>A uo 4381 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>A uo 4531 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (DESENVOLVIMENTO ECONÔMICO).</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>A uo 4631 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>A uo 4641 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>A uo 5261 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
         <is>
           <t>A uo 2311, 
 programa 7, 
@@ -8197,13 +7693,13 @@
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B612" t="inlineStr">
         <is>
           <t>A uo 1191, 
 programa 20, 
@@ -8212,13 +7708,13 @@
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B613" t="inlineStr">
         <is>
           <t>A uo 1371, 
 programa 21, 
@@ -8227,13 +7723,13 @@
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>A uo 2151, 
 programa 42, 
@@ -8242,13 +7738,13 @@
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>A uo 4291, 
 programa 60, 
@@ -8257,13 +7753,13 @@
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>A uo 1481, 
 programa 68, 
@@ -8272,13 +7768,13 @@
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B617" t="inlineStr">
         <is>
           <t>A uo 1481, 
 programa 83, 
@@ -8287,13 +7783,13 @@
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B618" t="inlineStr">
         <is>
           <t>A uo 1301, 
 programa 99, 
@@ -8302,13 +7798,13 @@
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>A uo 1491, 
 programa 119, 
@@ -8317,13 +7813,13 @@
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B620" t="inlineStr">
         <is>
           <t>A uo 1221, 
 programa 133, 
@@ -8332,13 +7828,13 @@
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B621" t="inlineStr">
         <is>
           <t>A uo 1251, 
 programa 136, 
@@ -8347,13 +7843,13 @@
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>A uo 1071, 
 programa 139, 
@@ -8362,13 +7858,13 @@
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B623" t="inlineStr">
         <is>
           <t>A uo 2481, 
 programa 161, 
@@ -8377,13 +7873,13 @@
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>A uo 1261, 
 programa 165, 
@@ -8392,13 +7888,13 @@
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t>check_valores_sigplan_programas</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>A uo 1501, 
 programa 705, 
@@ -8414,7 +7910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8466,7 +7962,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -8476,7 +7972,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -8506,7 +8002,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -8522,37 +8018,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>check_indicadores_justificativa_previsao_em_apuracao</t>
+          <t>check_intra_detalhamento</t>
         </is>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_exists</t>
+          <t>check_limite_ano0</t>
         </is>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>check_indicadores_previsoes_zeradas</t>
+          <t>check_objetivos_estrategicos_exists</t>
         </is>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>check_intra_despesa</t>
+          <t>check_ods_exists</t>
         </is>
       </c>
       <c r="B14">
@@ -8562,7 +8058,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>check_intra_detalhamento</t>
+          <t>check_repasse_recursos</t>
         </is>
       </c>
       <c r="B15">
@@ -8572,60 +8068,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>check_limite_ano0</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B16">
-        <v>517</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>check_objetivos_estrategicos_exists</t>
+          <t>check_valores_sigplan_programas</t>
         </is>
       </c>
       <c r="B17">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>check_ods_exists</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>check_repasse_recursos</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B21">
         <v>15</v>
       </c>
     </row>

--- a/data/checks-planejamento.xlsx
+++ b/data/checks-planejamento.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1471,231 +1471,6 @@
       <c r="B93" t="inlineStr">
         <is>
           <t>A uo 5261 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>A uo 2311, 
-programa 7, 
-área temática 03AT03 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 216.248.265,00) diferente da base ações-planejamento (R$ 151.136.947,00). Diferença de R$ -65111318.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>A uo 1191, 
-programa 20, 
-área temática 01AT01 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 13.239.000,00) diferente da base ações-planejamento (R$ 13.238.000,00). Diferença de R$ -1000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>A uo 1371, 
-programa 21, 
-área temática 11AT11 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 3.418.369.851,00) diferente da base ações-planejamento (R$ 115.369.851,00). Diferença de R$ -3.303e+09.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>A uo 2151, 
-programa 42, 
-área temática 03AT03 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 31.775.244,00) diferente da base ações-planejamento (R$ 31.765.244,00). Diferença de R$ -10000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>A uo 4291, 
-programa 60, 
-área temática 04AT04 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 702.771.556,00) diferente da base ações-planejamento (R$ 702.247.087,00). Diferença de R$ -524469.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>A uo 1481, 
-programa 68, 
-área temática 10AT10 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 40.387.963,00) diferente da base ações-planejamento (R$ 27.201.811,00). Diferença de R$ -13186152.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>A uo 1481, 
-programa 83, 
-área temática 10AT10 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 1.562.570,00) diferente da base ações-planejamento (R$ 1.233.792,00). Diferença de R$ -328778.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>A uo 1301, 
-programa 99, 
-área temática 05AT05 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 37.444.335,00) diferente da base ações-planejamento (R$ 36.529.088,00). Diferença de R$ -915247.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>A uo 1491, 
-programa 119, 
-área temática 12AT12 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 35.963.734,00) diferente da base ações-planejamento (R$ 35.962.734,00). Diferença de R$ -1000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>A uo 1221, 
-programa 133, 
-área temática 02AT02 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 498.121.008,00) diferente da base ações-planejamento (R$ 495.758.569,00). Diferença de R$ -2362439.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>A uo 1251, 
-programa 136, 
-área temática 03AT03 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 257.268.346,00) diferente da base ações-planejamento (R$ 257.267.346,00). Diferença de R$ -1000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>A uo 1071, 
-programa 139, 
-área temática 12AT12 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 207.973.317,00) diferente da base ações-planejamento (R$ 207.973.316,00). Diferença de R$ -1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>A uo 2481, 
-programa 161, 
-área temática 08AT08 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 406.412.088,00) diferente da base ações-planejamento (R$ 406.411.088,00). Diferença de R$ -1000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>A uo 1261, 
-programa 165, 
-área temática 03AT03 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 44.615.293,00) diferente da base ações-planejamento (R$ 43.575.293,00). Diferença de R$ -1040000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>A uo 1501, 
-programa 705, 
-área temática 08AT08 está com valor 
-de meta orçamentária do ano 0, base programas (R$ 72.198.856.106,00) diferente da base ações-planejamento (R$ 72.198.854.106,00). Diferença de R$ -2000.</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1861,16 +1636,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>check_valores_sigplan_programas</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/checks-planejamento.xlsx
+++ b/data/checks-planejamento.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A Fonte de Recurso 60 está com os valores totais de receita e despesa diferentes nas bases. R$ 4.506.993.690,00 na base orçamento fiscal da receita, e 5.326.603.517,00 na qdd fiscal. A diferença é de R$ -819609827.</t>
+          <t>A Fonte de Recurso 60 está com os valores totais de receita e despesa diferentes nas bases. R$ 4.506.993.690,00 na base orçamento fiscal da receita, e 3.692.974.668,00 na qdd fiscal. A diferença é de R$ 814019022.</t>
         </is>
       </c>
     </row>
@@ -1213,84 +1213,84 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A uo 1251, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 263.715.306,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+          <t>A uo 1301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A uo 1251, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 5.358.422,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+          <t>A uo 1917 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (FAZENDA).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 1.072.922.038,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+          <t>A uo 2301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A uo 1451, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 46.826.403,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+          <t>A uo 2431 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A uo 1451, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 910.719,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+          <t>A uo 2461 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A uo 1511, fonte 60, grupo 3, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 217.067.440,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+          <t>A uo 2471 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A uo 1511, fonte 60, grupo 4, ipu 2 está com valor de despesa na base qdd-fiscal (R$ 26.828.521,00) diferente do valor repassado para essa mesma uo  na base repasse-recursos (R$  NA). Diferença de R$  NA.</t>
+          <t>A uo 2481 está com setor divergente na base ações-planejamento (PLANEJAMENTO E GESTÃO) em relação à tabela auxiliar setor-governo da loa (NA).</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A uo 1301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+          <t>A uo 2781 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (PLANEJAMENTO E GESTÃO).</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A uo 1917 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (FAZENDA).</t>
+          <t>A uo 4171 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (AGRICULTURA, PECUÁRIA E ABASTECIMENTO).</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A uo 2301 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+          <t>A uo 4331 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A uo 2431 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+          <t>A uo 4381 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A uo 2461 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+          <t>A uo 4531 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (DESENVOLVIMENTO ECONÔMICO).</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>A uo 2471 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
+          <t>A uo 4631 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A uo 2481 está com setor divergente na base ações-planejamento (PLANEJAMENTO E GESTÃO) em relação à tabela auxiliar setor-governo da loa (NA).</t>
+          <t>A uo 4641 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
       </c>
     </row>
@@ -1385,90 +1385,6 @@
         </is>
       </c>
       <c r="B86" t="inlineStr">
-        <is>
-          <t>A uo 2781 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (PLANEJAMENTO E GESTÃO).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>A uo 4171 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (AGRICULTURA, PECUÁRIA E ABASTECIMENTO).</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>A uo 4331 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>A uo 4381 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>A uo 4531 está com setor divergente na base ações-planejamento (NA) em relação à tabela auxiliar setor-governo da loa (DESENVOLVIMENTO ECONÔMICO).</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>A uo 4631 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>A uo 4641 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
         <is>
           <t>A uo 5261 está com setor divergente na base ações-planejamento (INFRAESTRTURA, MOBILIDADE E PARCERIAS) em relação à tabela auxiliar setor-governo da loa (INFRAESTRUTURA, MOBILIDADE E PARCERIAS).</t>
         </is>
@@ -1481,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1619,20 +1535,10 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>check_repasse_recursos</t>
+          <t>check_setor_governo</t>
         </is>
       </c>
       <c r="B14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>check_setor_governo</t>
-        </is>
-      </c>
-      <c r="B15">
         <v>15</v>
       </c>
     </row>
